--- a/samples/예시데이터_모델별엑셀.xlsx
+++ b/samples/예시데이터_모델별엑셀.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,19 +449,16 @@
         <v>주행내구</v>
       </c>
       <c r="D3" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E3">
         <v>1240</v>
       </c>
       <c r="F3">
-        <v>1246</v>
+        <v>1247.5</v>
       </c>
       <c r="G3" t="str">
         <v>경유</v>
-      </c>
-      <c r="H3">
-        <v>17.6</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -481,10 +478,10 @@
         <v>주행내구</v>
       </c>
       <c r="D4" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E4">
-        <v>1246</v>
+        <v>1247.5</v>
       </c>
       <c r="F4">
         <v>1253</v>
@@ -493,7 +490,7 @@
         <v>경유</v>
       </c>
       <c r="H4">
-        <v>18.6</v>
+        <v>47.7</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -504,7 +501,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B5" t="str">
         <v>1호기</v>
@@ -513,19 +510,16 @@
         <v>주행내구</v>
       </c>
       <c r="D5" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E5">
         <v>1253</v>
       </c>
       <c r="F5">
-        <v>1260</v>
+        <v>1260.5</v>
       </c>
       <c r="G5" t="str">
         <v>경유</v>
-      </c>
-      <c r="H5">
-        <v>20.9</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -536,7 +530,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B6" t="str">
         <v>1호기</v>
@@ -545,19 +539,16 @@
         <v>주행내구</v>
       </c>
       <c r="D6" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E6">
-        <v>1260</v>
+        <v>1260.5</v>
       </c>
       <c r="F6">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G6" t="str">
         <v>경유</v>
-      </c>
-      <c r="H6">
-        <v>16.8</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -568,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-06</v>
       </c>
       <c r="B7" t="str">
         <v>1호기</v>
@@ -577,19 +568,19 @@
         <v>주행내구</v>
       </c>
       <c r="D7" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E7">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F7">
-        <v>1273.5</v>
+        <v>1272.5</v>
       </c>
       <c r="G7" t="str">
         <v>경유</v>
       </c>
       <c r="H7">
-        <v>19.8</v>
+        <v>45.5</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -600,7 +591,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B8" t="str">
         <v>1호기</v>
@@ -609,19 +600,16 @@
         <v>주행내구</v>
       </c>
       <c r="D8" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E8">
-        <v>1273.5</v>
+        <v>1272.5</v>
       </c>
       <c r="F8">
-        <v>1279.5</v>
+        <v>1280</v>
       </c>
       <c r="G8" t="str">
         <v>경유</v>
-      </c>
-      <c r="H8">
-        <v>15.7</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -632,7 +620,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B9" t="str">
         <v>1호기</v>
@@ -641,19 +629,16 @@
         <v>주행내구</v>
       </c>
       <c r="D9" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E9">
-        <v>1279.5</v>
+        <v>1280</v>
       </c>
       <c r="F9">
-        <v>1286.5</v>
+        <v>1285</v>
       </c>
       <c r="G9" t="str">
         <v>경유</v>
-      </c>
-      <c r="H9">
-        <v>18.1</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -664,7 +649,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B10" t="str">
         <v>1호기</v>
@@ -673,19 +658,16 @@
         <v>주행내구</v>
       </c>
       <c r="D10" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E10">
-        <v>1286.5</v>
+        <v>1285</v>
       </c>
       <c r="F10">
-        <v>1291.5</v>
+        <v>1292.5</v>
       </c>
       <c r="G10" t="str">
         <v>경유</v>
-      </c>
-      <c r="H10">
-        <v>14.6</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -696,7 +678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B11" t="str">
         <v>1호기</v>
@@ -705,30 +687,30 @@
         <v>주행내구</v>
       </c>
       <c r="D11" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E11">
-        <v>1291.5</v>
+        <v>1292.5</v>
       </c>
       <c r="F11">
-        <v>1299</v>
+        <v>1300.5</v>
       </c>
       <c r="G11" t="str">
         <v>경유</v>
       </c>
       <c r="H11">
-        <v>22.6</v>
+        <v>61.6</v>
       </c>
       <c r="I11" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>IMG_20260713_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B12" t="str">
         <v>1호기</v>
@@ -737,19 +719,16 @@
         <v>주행내구</v>
       </c>
       <c r="D12" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E12">
-        <v>1299</v>
+        <v>1300.5</v>
       </c>
       <c r="F12">
-        <v>1305</v>
+        <v>1306.5</v>
       </c>
       <c r="G12" t="str">
         <v>경유</v>
-      </c>
-      <c r="H12">
-        <v>15.6</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -760,7 +739,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B13" t="str">
         <v>1호기</v>
@@ -769,19 +748,16 @@
         <v>주행내구</v>
       </c>
       <c r="D13" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E13">
-        <v>1305</v>
+        <v>1306.5</v>
       </c>
       <c r="F13">
-        <v>1313</v>
+        <v>1314.5</v>
       </c>
       <c r="G13" t="str">
         <v>경유</v>
-      </c>
-      <c r="H13">
-        <v>24.5</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -792,7 +768,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B14" t="str">
         <v>1호기</v>
@@ -801,19 +777,19 @@
         <v>주행내구</v>
       </c>
       <c r="D14" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E14">
-        <v>1313</v>
+        <v>1314.5</v>
       </c>
       <c r="F14">
-        <v>1320</v>
+        <v>1321.5</v>
       </c>
       <c r="G14" t="str">
         <v>경유</v>
       </c>
       <c r="H14">
-        <v>20.1</v>
+        <v>60.2</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -824,7 +800,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B15" t="str">
         <v>1호기</v>
@@ -833,19 +809,16 @@
         <v>주행내구</v>
       </c>
       <c r="D15" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E15">
-        <v>1320</v>
+        <v>1321.5</v>
       </c>
       <c r="F15">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="G15" t="str">
         <v>경유</v>
-      </c>
-      <c r="H15">
-        <v>20.5</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -856,7 +829,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B16" t="str">
         <v>1호기</v>
@@ -865,19 +838,16 @@
         <v>주행내구</v>
       </c>
       <c r="D16" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E16">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="F16">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="G16" t="str">
         <v>경유</v>
-      </c>
-      <c r="H16">
-        <v>15.7</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -888,7 +858,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B17" t="str">
         <v>1호기</v>
@@ -897,19 +867,16 @@
         <v>주행내구</v>
       </c>
       <c r="D17" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E17">
-        <v>1321</v>
+        <v>1335</v>
       </c>
       <c r="F17">
-        <v>1326.5</v>
+        <v>1340.5</v>
       </c>
       <c r="G17" t="str">
         <v>경유</v>
-      </c>
-      <c r="H17">
-        <v>16.7</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -920,7 +887,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B18" t="str">
         <v>1호기</v>
@@ -929,19 +896,19 @@
         <v>주행내구</v>
       </c>
       <c r="D18" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E18">
-        <v>1326.5</v>
+        <v>1340.5</v>
       </c>
       <c r="F18">
-        <v>1332</v>
+        <v>1346</v>
       </c>
       <c r="G18" t="str">
         <v>경유</v>
       </c>
       <c r="H18">
-        <v>16.3</v>
+        <v>48.8</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,7 +919,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B19" t="str">
         <v>1호기</v>
@@ -961,30 +928,27 @@
         <v>주행내구</v>
       </c>
       <c r="D19" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E19">
-        <v>1332</v>
+        <v>1346</v>
       </c>
       <c r="F19">
-        <v>1337.5</v>
+        <v>1351.5</v>
       </c>
       <c r="G19" t="str">
         <v>경유</v>
       </c>
-      <c r="H19">
-        <v>16.4</v>
-      </c>
       <c r="I19" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J19" t="str">
-        <v>IMG_20260723_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B20" t="str">
         <v>1호기</v>
@@ -993,30 +957,27 @@
         <v>주행내구</v>
       </c>
       <c r="D20" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E20">
-        <v>1337.5</v>
+        <v>1351.5</v>
       </c>
       <c r="F20">
-        <v>1342.5</v>
+        <v>1358.5</v>
       </c>
       <c r="G20" t="str">
         <v>경유</v>
       </c>
-      <c r="H20">
-        <v>12.9</v>
-      </c>
       <c r="I20" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
       <c r="J20" t="str">
-        <v>IMG_20260724_1(예시).jpg</v>
+        <v>IMG_20260717_1(예시).jpg</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-20</v>
       </c>
       <c r="B21" t="str">
         <v>1호기</v>
@@ -1025,19 +986,19 @@
         <v>주행내구</v>
       </c>
       <c r="D21" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E21">
-        <v>1342.5</v>
+        <v>1358.5</v>
       </c>
       <c r="F21">
-        <v>1350</v>
+        <v>1364</v>
       </c>
       <c r="G21" t="str">
         <v>경유</v>
       </c>
       <c r="H21">
-        <v>21.3</v>
+        <v>49</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1048,7 +1009,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B22" t="str">
         <v>1호기</v>
@@ -1057,19 +1018,16 @@
         <v>주행내구</v>
       </c>
       <c r="D22" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E22">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="F22">
-        <v>1356.5</v>
+        <v>1358.5</v>
       </c>
       <c r="G22" t="str">
         <v>경유</v>
-      </c>
-      <c r="H22">
-        <v>17</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1080,7 +1038,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B23" t="str">
         <v>1호기</v>
@@ -1089,19 +1047,16 @@
         <v>주행내구</v>
       </c>
       <c r="D23" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E23">
-        <v>1356.5</v>
+        <v>1358.5</v>
       </c>
       <c r="F23">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="G23" t="str">
         <v>경유</v>
-      </c>
-      <c r="H23">
-        <v>18.1</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1112,7 +1067,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-22</v>
       </c>
       <c r="B24" t="str">
         <v>1호기</v>
@@ -1121,19 +1076,16 @@
         <v>주행내구</v>
       </c>
       <c r="D24" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E24">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="F24">
-        <v>1370.5</v>
+        <v>1371</v>
       </c>
       <c r="G24" t="str">
         <v>경유</v>
-      </c>
-      <c r="H24">
-        <v>20.8</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1144,7 +1096,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-07-31</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B25" t="str">
         <v>1호기</v>
@@ -1153,19 +1105,19 @@
         <v>주행내구</v>
       </c>
       <c r="D25" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E25">
-        <v>1370.5</v>
+        <v>1371</v>
       </c>
       <c r="F25">
-        <v>1377.5</v>
+        <v>1377</v>
       </c>
       <c r="G25" t="str">
         <v>경유</v>
       </c>
       <c r="H25">
-        <v>20.6</v>
+        <v>52.3</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1176,7 +1128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-08-03</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B26" t="str">
         <v>1호기</v>
@@ -1185,19 +1137,16 @@
         <v>주행내구</v>
       </c>
       <c r="D26" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E26">
-        <v>1377.5</v>
+        <v>1377</v>
       </c>
       <c r="F26">
-        <v>1385.5</v>
+        <v>1383</v>
       </c>
       <c r="G26" t="str">
         <v>경유</v>
-      </c>
-      <c r="H26">
-        <v>24.4</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1208,7 +1157,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-08-04</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B27" t="str">
         <v>1호기</v>
@@ -1217,19 +1166,16 @@
         <v>주행내구</v>
       </c>
       <c r="D27" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E27">
-        <v>1385.5</v>
+        <v>1383</v>
       </c>
       <c r="F27">
-        <v>1392</v>
+        <v>1390.5</v>
       </c>
       <c r="G27" t="str">
         <v>경유</v>
-      </c>
-      <c r="H27">
-        <v>17.4</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1240,7 +1186,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-08-05</v>
+        <v>2026-07-27</v>
       </c>
       <c r="B28" t="str">
         <v>1호기</v>
@@ -1249,10 +1195,10 @@
         <v>주행내구</v>
       </c>
       <c r="D28" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E28">
-        <v>1392</v>
+        <v>1390.5</v>
       </c>
       <c r="F28">
         <v>1398</v>
@@ -1261,7 +1207,7 @@
         <v>경유</v>
       </c>
       <c r="H28">
-        <v>15.9</v>
+        <v>60.9</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1272,7 +1218,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-08-06</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B29" t="str">
         <v>1호기</v>
@@ -1281,7 +1227,7 @@
         <v>주행내구</v>
       </c>
       <c r="D29" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E29">
         <v>1398</v>
@@ -1292,9 +1238,6 @@
       <c r="G29" t="str">
         <v>경유</v>
       </c>
-      <c r="H29">
-        <v>15.1</v>
-      </c>
       <c r="I29" t="str">
         <v/>
       </c>
@@ -1304,7 +1247,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-08-07</v>
+        <v>2026-07-28</v>
       </c>
       <c r="B30" t="str">
         <v>1호기</v>
@@ -1313,7 +1256,7 @@
         <v>주행내구</v>
       </c>
       <c r="D30" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E30">
         <v>1403.5</v>
@@ -1324,9 +1267,6 @@
       <c r="G30" t="str">
         <v>경유</v>
       </c>
-      <c r="H30">
-        <v>20.1</v>
-      </c>
       <c r="I30" t="str">
         <v/>
       </c>
@@ -1336,7 +1276,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-08-10</v>
+        <v>2026-07-29</v>
       </c>
       <c r="B31" t="str">
         <v>1호기</v>
@@ -1345,19 +1285,16 @@
         <v>주행내구</v>
       </c>
       <c r="D31" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E31">
         <v>1411</v>
       </c>
       <c r="F31">
-        <v>1419</v>
+        <v>1417.5</v>
       </c>
       <c r="G31" t="str">
         <v>경유</v>
-      </c>
-      <c r="H31">
-        <v>20.9</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1368,7 +1305,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-08-11</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B32" t="str">
         <v>1호기</v>
@@ -1377,19 +1314,19 @@
         <v>주행내구</v>
       </c>
       <c r="D32" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E32">
-        <v>1419</v>
+        <v>1417.5</v>
       </c>
       <c r="F32">
-        <v>1426.5</v>
+        <v>1423</v>
       </c>
       <c r="G32" t="str">
         <v>경유</v>
       </c>
       <c r="H32">
-        <v>22.3</v>
+        <v>49.3</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1400,7 +1337,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-08-12</v>
+        <v>2026-07-30</v>
       </c>
       <c r="B33" t="str">
         <v>1호기</v>
@@ -1409,19 +1346,16 @@
         <v>주행내구</v>
       </c>
       <c r="D33" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E33">
-        <v>1426.5</v>
+        <v>1423</v>
       </c>
       <c r="F33">
-        <v>1431.5</v>
+        <v>1428.5</v>
       </c>
       <c r="G33" t="str">
         <v>경유</v>
-      </c>
-      <c r="H33">
-        <v>14.8</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1432,7 +1366,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-08-13</v>
+        <v>2026-07-31</v>
       </c>
       <c r="B34" t="str">
         <v>1호기</v>
@@ -1441,19 +1375,16 @@
         <v>주행내구</v>
       </c>
       <c r="D34" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E34">
-        <v>1431.5</v>
+        <v>1428.5</v>
       </c>
       <c r="F34">
-        <v>1439.5</v>
+        <v>1436</v>
       </c>
       <c r="G34" t="str">
         <v>경유</v>
-      </c>
-      <c r="H34">
-        <v>21.3</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1464,7 +1395,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-03</v>
       </c>
       <c r="B35" t="str">
         <v>1호기</v>
@@ -1473,19 +1404,19 @@
         <v>주행내구</v>
       </c>
       <c r="D35" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E35">
-        <v>1439.5</v>
+        <v>1436</v>
       </c>
       <c r="F35">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="G35" t="str">
         <v>경유</v>
       </c>
       <c r="H35">
-        <v>18</v>
+        <v>50.2</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1496,7 +1427,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B36" t="str">
         <v>1호기</v>
@@ -1505,19 +1436,16 @@
         <v>주행내구</v>
       </c>
       <c r="D36" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E36">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="F36">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="G36" t="str">
         <v>경유</v>
-      </c>
-      <c r="H36">
-        <v>15.2</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1528,7 +1456,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-04</v>
       </c>
       <c r="B37" t="str">
         <v>1호기</v>
@@ -1537,19 +1465,16 @@
         <v>주행내구</v>
       </c>
       <c r="D37" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E37">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="F37">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="G37" t="str">
         <v>경유</v>
-      </c>
-      <c r="H37">
-        <v>21.5</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1560,7 +1485,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-05</v>
       </c>
       <c r="B38" t="str">
         <v>1호기</v>
@@ -1569,30 +1494,27 @@
         <v>주행내구</v>
       </c>
       <c r="D38" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E38">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="F38">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="G38" t="str">
         <v>경유</v>
       </c>
-      <c r="H38">
-        <v>12.9</v>
-      </c>
       <c r="I38" t="str">
-        <v/>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>IMG_20260805_1(예시).jpg</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-08-20</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B39" t="str">
         <v>1호기</v>
@@ -1601,19 +1523,19 @@
         <v>주행내구</v>
       </c>
       <c r="D39" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E39">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="F39">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="G39" t="str">
         <v>경유</v>
       </c>
       <c r="H39">
-        <v>13.6</v>
+        <v>40.9</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1624,7 +1546,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-06</v>
       </c>
       <c r="B40" t="str">
         <v>1호기</v>
@@ -1633,19 +1555,16 @@
         <v>주행내구</v>
       </c>
       <c r="D40" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E40">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="F40">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G40" t="str">
         <v>경유</v>
-      </c>
-      <c r="H40">
-        <v>22.4</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1656,7 +1575,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-08-24</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B41" t="str">
         <v>1호기</v>
@@ -1665,19 +1584,16 @@
         <v>주행내구</v>
       </c>
       <c r="D41" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E41">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F41">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="G41" t="str">
         <v>경유</v>
-      </c>
-      <c r="H41">
-        <v>18.1</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1688,7 +1604,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-08-25</v>
+        <v>2026-08-10</v>
       </c>
       <c r="B42" t="str">
         <v>1호기</v>
@@ -1697,19 +1613,19 @@
         <v>주행내구</v>
       </c>
       <c r="D42" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E42">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="F42">
-        <v>1490.5</v>
+        <v>1488.5</v>
       </c>
       <c r="G42" t="str">
         <v>경유</v>
       </c>
       <c r="H42">
-        <v>19.8</v>
+        <v>59.5</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1720,7 +1636,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-08-26</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B43" t="str">
         <v>1호기</v>
@@ -1729,19 +1645,16 @@
         <v>주행내구</v>
       </c>
       <c r="D43" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E43">
-        <v>1490.5</v>
+        <v>1488.5</v>
       </c>
       <c r="F43">
-        <v>1496.5</v>
+        <v>1493.5</v>
       </c>
       <c r="G43" t="str">
         <v>경유</v>
-      </c>
-      <c r="H43">
-        <v>15.5</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1752,7 +1665,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-08-27</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B44" t="str">
         <v>1호기</v>
@@ -1761,19 +1674,16 @@
         <v>주행내구</v>
       </c>
       <c r="D44" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E44">
-        <v>1496.5</v>
+        <v>1493.5</v>
       </c>
       <c r="F44">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="G44" t="str">
         <v>경유</v>
-      </c>
-      <c r="H44">
-        <v>19.6</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1784,7 +1694,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-08-28</v>
+        <v>2026-08-12</v>
       </c>
       <c r="B45" t="str">
         <v>1호기</v>
@@ -1793,30 +1703,27 @@
         <v>주행내구</v>
       </c>
       <c r="D45" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E45">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="F45">
-        <v>1511.5</v>
+        <v>1508.5</v>
       </c>
       <c r="G45" t="str">
         <v>경유</v>
       </c>
-      <c r="H45">
-        <v>22.5</v>
-      </c>
       <c r="I45" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J45" t="str">
-        <v>IMG_20260828_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-08-31</v>
+        <v>2026-08-13</v>
       </c>
       <c r="B46" t="str">
         <v>1호기</v>
@@ -1825,30 +1732,30 @@
         <v>주행내구</v>
       </c>
       <c r="D46" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E46">
-        <v>1511.5</v>
+        <v>1508.5</v>
       </c>
       <c r="F46">
-        <v>1519.5</v>
+        <v>1514.5</v>
       </c>
       <c r="G46" t="str">
         <v>경유</v>
       </c>
       <c r="H46">
-        <v>20.2</v>
+        <v>54.5</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>IMG_20260813_1(예시).jpg</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-09-01</v>
+        <v>2026-08-13</v>
       </c>
       <c r="B47" t="str">
         <v>1호기</v>
@@ -1857,19 +1764,16 @@
         <v>주행내구</v>
       </c>
       <c r="D47" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E47">
-        <v>1519.5</v>
+        <v>1514.5</v>
       </c>
       <c r="F47">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="G47" t="str">
         <v>경유</v>
-      </c>
-      <c r="H47">
-        <v>19.4</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1880,7 +1784,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-09-02</v>
+        <v>2026-08-14</v>
       </c>
       <c r="B48" t="str">
         <v>1호기</v>
@@ -1889,30 +1793,27 @@
         <v>주행내구</v>
       </c>
       <c r="D48" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E48">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F48">
-        <v>1532.5</v>
+        <v>1527.5</v>
       </c>
       <c r="G48" t="str">
         <v>경유</v>
       </c>
-      <c r="H48">
-        <v>17</v>
-      </c>
       <c r="I48" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J48" t="str">
-        <v>IMG_20260902_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-09-03</v>
+        <v>2026-08-17</v>
       </c>
       <c r="B49" t="str">
         <v>1호기</v>
@@ -1921,19 +1822,19 @@
         <v>주행내구</v>
       </c>
       <c r="D49" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E49">
+        <v>1527.5</v>
+      </c>
+      <c r="F49">
         <v>1532.5</v>
       </c>
-      <c r="F49">
-        <v>1540</v>
-      </c>
       <c r="G49" t="str">
         <v>경유</v>
       </c>
       <c r="H49">
-        <v>22.5</v>
+        <v>43.9</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1944,7 +1845,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-09-04</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B50" t="str">
         <v>1호기</v>
@@ -1953,19 +1854,16 @@
         <v>주행내구</v>
       </c>
       <c r="D50" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E50">
-        <v>1540</v>
+        <v>1532.5</v>
       </c>
       <c r="F50">
-        <v>1545</v>
+        <v>1537.5</v>
       </c>
       <c r="G50" t="str">
         <v>경유</v>
-      </c>
-      <c r="H50">
-        <v>14</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1976,7 +1874,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-09-07</v>
+        <v>2026-08-18</v>
       </c>
       <c r="B51" t="str">
         <v>1호기</v>
@@ -1985,30 +1883,27 @@
         <v>주행내구</v>
       </c>
       <c r="D51" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E51">
-        <v>1545</v>
+        <v>1537.5</v>
       </c>
       <c r="F51">
-        <v>1550</v>
+        <v>1543.5</v>
       </c>
       <c r="G51" t="str">
         <v>경유</v>
       </c>
-      <c r="H51">
-        <v>14</v>
-      </c>
       <c r="I51" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>IMG_20260818_1(예시).jpg</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-09-08</v>
+        <v>2026-08-19</v>
       </c>
       <c r="B52" t="str">
         <v>1호기</v>
@@ -2017,19 +1912,16 @@
         <v>주행내구</v>
       </c>
       <c r="D52" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E52">
-        <v>1550</v>
+        <v>1543.5</v>
       </c>
       <c r="F52">
-        <v>1557</v>
+        <v>1550.5</v>
       </c>
       <c r="G52" t="str">
         <v>경유</v>
-      </c>
-      <c r="H52">
-        <v>18.3</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2040,7 +1932,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-09-09</v>
+        <v>2026-08-20</v>
       </c>
       <c r="B53" t="str">
         <v>1호기</v>
@@ -2049,19 +1941,19 @@
         <v>주행내구</v>
       </c>
       <c r="D53" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E53">
-        <v>1557</v>
+        <v>1550.5</v>
       </c>
       <c r="F53">
-        <v>1564</v>
+        <v>1557.5</v>
       </c>
       <c r="G53" t="str">
         <v>경유</v>
       </c>
       <c r="H53">
-        <v>19.8</v>
+        <v>59.4</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2072,7 +1964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-09-10</v>
+        <v>2026-08-20</v>
       </c>
       <c r="B54" t="str">
         <v>1호기</v>
@@ -2081,19 +1973,16 @@
         <v>주행내구</v>
       </c>
       <c r="D54" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E54">
-        <v>1564</v>
+        <v>1557.5</v>
       </c>
       <c r="F54">
-        <v>1571</v>
+        <v>1564.5</v>
       </c>
       <c r="G54" t="str">
         <v>경유</v>
-      </c>
-      <c r="H54">
-        <v>19.4</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2104,7 +1993,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-09-11</v>
+        <v>2026-08-21</v>
       </c>
       <c r="B55" t="str">
         <v>1호기</v>
@@ -2113,30 +2002,27 @@
         <v>주행내구</v>
       </c>
       <c r="D55" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E55">
-        <v>1571</v>
+        <v>1564.5</v>
       </c>
       <c r="F55">
-        <v>1578</v>
+        <v>1571.5</v>
       </c>
       <c r="G55" t="str">
         <v>경유</v>
       </c>
-      <c r="H55">
-        <v>18.1</v>
-      </c>
       <c r="I55" t="str">
-        <v/>
+        <v>충전 커넥터 체결 불량(예시)</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>IMG_20260821_1(예시).jpg</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-09-14</v>
+        <v>2026-08-24</v>
       </c>
       <c r="B56" t="str">
         <v>1호기</v>
@@ -2145,19 +2031,19 @@
         <v>주행내구</v>
       </c>
       <c r="D56" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E56">
-        <v>1578</v>
+        <v>1571.5</v>
       </c>
       <c r="F56">
-        <v>1585</v>
+        <v>1578.5</v>
       </c>
       <c r="G56" t="str">
         <v>경유</v>
       </c>
       <c r="H56">
-        <v>20.4</v>
+        <v>55</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2168,7 +2054,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-09-15</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B57" t="str">
         <v>1호기</v>
@@ -2177,19 +2063,16 @@
         <v>주행내구</v>
       </c>
       <c r="D57" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E57">
-        <v>1585</v>
+        <v>1578.5</v>
       </c>
       <c r="F57">
-        <v>1592.5</v>
+        <v>1584.5</v>
       </c>
       <c r="G57" t="str">
         <v>경유</v>
-      </c>
-      <c r="H57">
-        <v>18.9</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2200,7 +2083,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-09-16</v>
+        <v>2026-08-25</v>
       </c>
       <c r="B58" t="str">
         <v>1호기</v>
@@ -2209,19 +2092,16 @@
         <v>주행내구</v>
       </c>
       <c r="D58" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E58">
+        <v>1584.5</v>
+      </c>
+      <c r="F58">
         <v>1592.5</v>
       </c>
-      <c r="F58">
-        <v>1598.5</v>
-      </c>
       <c r="G58" t="str">
         <v>경유</v>
-      </c>
-      <c r="H58">
-        <v>18.4</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2232,7 +2112,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-09-17</v>
+        <v>2026-08-26</v>
       </c>
       <c r="B59" t="str">
         <v>1호기</v>
@@ -2241,19 +2121,16 @@
         <v>주행내구</v>
       </c>
       <c r="D59" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E59">
-        <v>1598.5</v>
+        <v>1592.5</v>
       </c>
       <c r="F59">
-        <v>1606.5</v>
+        <v>1599.5</v>
       </c>
       <c r="G59" t="str">
         <v>경유</v>
-      </c>
-      <c r="H59">
-        <v>23</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2264,7 +2141,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026-09-18</v>
+        <v>2026-08-27</v>
       </c>
       <c r="B60" t="str">
         <v>1호기</v>
@@ -2273,30 +2150,30 @@
         <v>주행내구</v>
       </c>
       <c r="D60" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E60">
-        <v>1606.5</v>
+        <v>1599.5</v>
       </c>
       <c r="F60">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="G60" t="str">
         <v>경유</v>
       </c>
       <c r="H60">
-        <v>15.3</v>
+        <v>53.6</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>IMG_20260827_1(예시).jpg</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-09-21</v>
+        <v>2026-08-27</v>
       </c>
       <c r="B61" t="str">
         <v>1호기</v>
@@ -2305,30 +2182,27 @@
         <v>주행내구</v>
       </c>
       <c r="D61" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E61">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="F61">
-        <v>1617</v>
+        <v>1611</v>
       </c>
       <c r="G61" t="str">
         <v>경유</v>
       </c>
-      <c r="H61">
-        <v>14.7</v>
-      </c>
       <c r="I61" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v>운전석 계기판 화면 깜빡임(예시)</v>
       </c>
       <c r="J61" t="str">
-        <v>IMG_20260921_1(예시).jpg</v>
+        <v>IMG_20260827_1(예시).jpg</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-09-22</v>
+        <v>2026-08-28</v>
       </c>
       <c r="B62" t="str">
         <v>1호기</v>
@@ -2337,19 +2211,16 @@
         <v>주행내구</v>
       </c>
       <c r="D62" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E62">
-        <v>1617</v>
+        <v>1611</v>
       </c>
       <c r="F62">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="G62" t="str">
         <v>경유</v>
-      </c>
-      <c r="H62">
-        <v>16.9</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2360,7 +2231,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-09-23</v>
+        <v>2026-08-31</v>
       </c>
       <c r="B63" t="str">
         <v>1호기</v>
@@ -2369,19 +2240,19 @@
         <v>주행내구</v>
       </c>
       <c r="D63" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E63">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="F63">
-        <v>1630.5</v>
+        <v>1624.5</v>
       </c>
       <c r="G63" t="str">
         <v>경유</v>
       </c>
       <c r="H63">
-        <v>19</v>
+        <v>44.9</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2392,7 +2263,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-01</v>
       </c>
       <c r="B64" t="str">
         <v>1호기</v>
@@ -2401,19 +2272,16 @@
         <v>주행내구</v>
       </c>
       <c r="D64" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E64">
-        <v>1630.5</v>
+        <v>1624.5</v>
       </c>
       <c r="F64">
-        <v>1636.5</v>
+        <v>1632</v>
       </c>
       <c r="G64" t="str">
         <v>경유</v>
-      </c>
-      <c r="H64">
-        <v>17.7</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2424,39 +2292,782 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="B65" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C65" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D65" t="str">
+        <v>운전자D</v>
+      </c>
+      <c r="E65">
+        <v>1632</v>
+      </c>
+      <c r="F65">
+        <v>1638</v>
+      </c>
+      <c r="G65" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-09-02</v>
+      </c>
+      <c r="B66" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C66" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D66" t="str">
+        <v>운전자C</v>
+      </c>
+      <c r="E66">
+        <v>1638</v>
+      </c>
+      <c r="F66">
+        <v>1643</v>
+      </c>
+      <c r="G66" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I66" t="str">
+        <v>충전 커넥터 체결 불량(예시)</v>
+      </c>
+      <c r="J66" t="str">
+        <v>IMG_20260902_1(예시).jpg</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-09-03</v>
+      </c>
+      <c r="B67" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C67" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D67" t="str">
+        <v>운전자D</v>
+      </c>
+      <c r="E67">
+        <v>1643</v>
+      </c>
+      <c r="F67">
+        <v>1650</v>
+      </c>
+      <c r="G67" t="str">
+        <v>경유</v>
+      </c>
+      <c r="H67">
+        <v>57.2</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-09-03</v>
+      </c>
+      <c r="B68" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C68" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D68" t="str">
+        <v>운전자B</v>
+      </c>
+      <c r="E68">
+        <v>1650</v>
+      </c>
+      <c r="F68">
+        <v>1656</v>
+      </c>
+      <c r="G68" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-09-04</v>
+      </c>
+      <c r="B69" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C69" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D69" t="str">
+        <v>운전자A</v>
+      </c>
+      <c r="E69">
+        <v>1656</v>
+      </c>
+      <c r="F69">
+        <v>1662.5</v>
+      </c>
+      <c r="G69" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="B70" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C70" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D70" t="str">
+        <v>운전자B</v>
+      </c>
+      <c r="E70">
+        <v>1662.5</v>
+      </c>
+      <c r="F70">
+        <v>1668.5</v>
+      </c>
+      <c r="G70" t="str">
+        <v>경유</v>
+      </c>
+      <c r="H70">
+        <v>50.6</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="B71" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C71" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D71" t="str">
+        <v>운전자C</v>
+      </c>
+      <c r="E71">
+        <v>1668.5</v>
+      </c>
+      <c r="F71">
+        <v>1675.5</v>
+      </c>
+      <c r="G71" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="B72" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C72" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D72" t="str">
+        <v>운전자A</v>
+      </c>
+      <c r="E72">
+        <v>1675.5</v>
+      </c>
+      <c r="F72">
+        <v>1682.5</v>
+      </c>
+      <c r="G72" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I72" t="str">
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+      </c>
+      <c r="J72" t="str">
+        <v>IMG_20260908_1(예시).jpg</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="B73" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C73" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D73" t="str">
+        <v>운전자D</v>
+      </c>
+      <c r="E73">
+        <v>1682.5</v>
+      </c>
+      <c r="F73">
+        <v>1689</v>
+      </c>
+      <c r="G73" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="B74" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C74" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D74" t="str">
+        <v>운전자A</v>
+      </c>
+      <c r="E74">
+        <v>1689</v>
+      </c>
+      <c r="F74">
+        <v>1696.5</v>
+      </c>
+      <c r="G74" t="str">
+        <v>경유</v>
+      </c>
+      <c r="H74">
+        <v>58</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="B75" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C75" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D75" t="str">
+        <v>운전자C</v>
+      </c>
+      <c r="E75">
+        <v>1696.5</v>
+      </c>
+      <c r="F75">
+        <v>1701.5</v>
+      </c>
+      <c r="G75" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="B76" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C76" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D76" t="str">
+        <v>운전자B</v>
+      </c>
+      <c r="E76">
+        <v>1701.5</v>
+      </c>
+      <c r="F76">
+        <v>1708</v>
+      </c>
+      <c r="G76" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="B77" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C77" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D77" t="str">
+        <v>운전자C</v>
+      </c>
+      <c r="E77">
+        <v>1708</v>
+      </c>
+      <c r="F77">
+        <v>1713.5</v>
+      </c>
+      <c r="G77" t="str">
+        <v>경유</v>
+      </c>
+      <c r="H77">
+        <v>46.6</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="B78" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C78" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D78" t="str">
+        <v>운전자D</v>
+      </c>
+      <c r="E78">
+        <v>1713.5</v>
+      </c>
+      <c r="F78">
+        <v>1720</v>
+      </c>
+      <c r="G78" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I78" t="str">
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+      </c>
+      <c r="J78" t="str">
+        <v>IMG_20260915_1(예시).jpg</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="B79" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C79" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D79" t="str">
+        <v>운전자B</v>
+      </c>
+      <c r="E79">
+        <v>1720</v>
+      </c>
+      <c r="F79">
+        <v>1726</v>
+      </c>
+      <c r="G79" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="B80" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C80" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D80" t="str">
+        <v>운전자A</v>
+      </c>
+      <c r="E80">
+        <v>1726</v>
+      </c>
+      <c r="F80">
+        <v>1731.5</v>
+      </c>
+      <c r="G80" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="B81" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C81" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D81" t="str">
+        <v>운전자B</v>
+      </c>
+      <c r="E81">
+        <v>1731.5</v>
+      </c>
+      <c r="F81">
+        <v>1739</v>
+      </c>
+      <c r="G81" t="str">
+        <v>경유</v>
+      </c>
+      <c r="H81">
+        <v>58.4</v>
+      </c>
+      <c r="I81" t="str">
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+      </c>
+      <c r="J81" t="str">
+        <v>IMG_20260917_1(예시).jpg</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="B82" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C82" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D82" t="str">
+        <v>운전자D</v>
+      </c>
+      <c r="E82">
+        <v>1739</v>
+      </c>
+      <c r="F82">
+        <v>1744.5</v>
+      </c>
+      <c r="G82" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I82" t="str">
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+      </c>
+      <c r="J82" t="str">
+        <v>IMG_20260917_1(예시).jpg</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="B83" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C83" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D83" t="str">
+        <v>운전자C</v>
+      </c>
+      <c r="E83">
+        <v>1744.5</v>
+      </c>
+      <c r="F83">
+        <v>1751.5</v>
+      </c>
+      <c r="G83" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="B84" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C84" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D84" t="str">
+        <v>운전자D</v>
+      </c>
+      <c r="E84">
+        <v>1751.5</v>
+      </c>
+      <c r="F84">
+        <v>1757</v>
+      </c>
+      <c r="G84" t="str">
+        <v>경유</v>
+      </c>
+      <c r="H84">
+        <v>47</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="B85" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C85" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D85" t="str">
+        <v>운전자A</v>
+      </c>
+      <c r="E85">
+        <v>1757</v>
+      </c>
+      <c r="F85">
+        <v>1765</v>
+      </c>
+      <c r="G85" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="B86" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C86" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D86" t="str">
+        <v>운전자C</v>
+      </c>
+      <c r="E86">
+        <v>1765</v>
+      </c>
+      <c r="F86">
+        <v>1772</v>
+      </c>
+      <c r="G86" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="B87" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C87" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D87" t="str">
+        <v>운전자B</v>
+      </c>
+      <c r="E87">
+        <v>1772</v>
+      </c>
+      <c r="F87">
+        <v>1777.5</v>
+      </c>
+      <c r="G87" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="B88" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C88" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D88" t="str">
+        <v>운전자C</v>
+      </c>
+      <c r="E88">
+        <v>1777.5</v>
+      </c>
+      <c r="F88">
+        <v>1782.5</v>
+      </c>
+      <c r="G88" t="str">
+        <v>경유</v>
+      </c>
+      <c r="H88">
+        <v>42.8</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2026-09-24</v>
+      </c>
+      <c r="B89" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C89" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D89" t="str">
+        <v>운전자A</v>
+      </c>
+      <c r="E89">
+        <v>1782.5</v>
+      </c>
+      <c r="F89">
+        <v>1788.5</v>
+      </c>
+      <c r="G89" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
         <v>2026-09-25</v>
       </c>
-      <c r="B65" t="str">
-        <v>1호기</v>
-      </c>
-      <c r="C65" t="str">
-        <v>주행내구</v>
-      </c>
-      <c r="D65" t="str">
-        <v>예시 운전자A</v>
-      </c>
-      <c r="E65">
-        <v>1636.5</v>
-      </c>
-      <c r="F65">
-        <v>1644</v>
-      </c>
-      <c r="G65" t="str">
-        <v>경유</v>
-      </c>
-      <c r="H65">
-        <v>23</v>
-      </c>
-      <c r="I65" t="str">
-        <v/>
-      </c>
-      <c r="J65" t="str">
+      <c r="B90" t="str">
+        <v>1호기</v>
+      </c>
+      <c r="C90" t="str">
+        <v>주행내구</v>
+      </c>
+      <c r="D90" t="str">
+        <v>운전자D</v>
+      </c>
+      <c r="E90">
+        <v>1788.5</v>
+      </c>
+      <c r="F90">
+        <v>1794</v>
+      </c>
+      <c r="G90" t="str">
+        <v>경유</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J90"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2513,25 +3124,22 @@
         <v>하역내구</v>
       </c>
       <c r="D3" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E3">
         <v>856.5</v>
       </c>
       <c r="F3">
-        <v>862.5</v>
+        <v>861.5</v>
       </c>
       <c r="G3" t="str">
         <v>LPG</v>
       </c>
-      <c r="H3">
-        <v>17.8</v>
-      </c>
       <c r="I3" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>IMG_20260701_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -2545,19 +3153,19 @@
         <v>하역내구</v>
       </c>
       <c r="D4" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E4">
-        <v>862.5</v>
+        <v>861.5</v>
       </c>
       <c r="F4">
-        <v>870.5</v>
+        <v>866.5</v>
       </c>
       <c r="G4" t="str">
         <v>LPG</v>
       </c>
       <c r="H4">
-        <v>23.7</v>
+        <v>47.1</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -2577,19 +3185,16 @@
         <v>하역내구</v>
       </c>
       <c r="D5" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E5">
-        <v>870.5</v>
+        <v>866.5</v>
       </c>
       <c r="F5">
-        <v>876.5</v>
+        <v>872</v>
       </c>
       <c r="G5" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H5">
-        <v>18.4</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -2609,19 +3214,19 @@
         <v>하역내구</v>
       </c>
       <c r="D6" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E6">
-        <v>876.5</v>
+        <v>872</v>
       </c>
       <c r="F6">
-        <v>883.5</v>
+        <v>877</v>
       </c>
       <c r="G6" t="str">
         <v>LPG</v>
       </c>
       <c r="H6">
-        <v>19.9</v>
+        <v>49.3</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -2641,19 +3246,16 @@
         <v>하역내구</v>
       </c>
       <c r="D7" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E7">
+        <v>877</v>
+      </c>
+      <c r="F7">
         <v>883.5</v>
-      </c>
-      <c r="F7">
-        <v>891</v>
       </c>
       <c r="G7" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H7">
-        <v>22.4</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -2673,25 +3275,22 @@
         <v>하역내구</v>
       </c>
       <c r="D8" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E8">
-        <v>891</v>
+        <v>883.5</v>
       </c>
       <c r="F8">
-        <v>897.5</v>
+        <v>890</v>
       </c>
       <c r="G8" t="str">
         <v>LPG</v>
       </c>
-      <c r="H8">
-        <v>19.9</v>
-      </c>
       <c r="I8" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>IMG_20260708_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2705,25 +3304,25 @@
         <v>하역내구</v>
       </c>
       <c r="D9" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E9">
-        <v>897.5</v>
+        <v>890</v>
       </c>
       <c r="F9">
-        <v>904.5</v>
+        <v>897</v>
       </c>
       <c r="G9" t="str">
         <v>LPG</v>
       </c>
       <c r="H9">
-        <v>22.3</v>
+        <v>58.7</v>
       </c>
       <c r="I9" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>IMG_20260709_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2737,19 +3336,16 @@
         <v>하역내구</v>
       </c>
       <c r="D10" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E10">
-        <v>904.5</v>
+        <v>897</v>
       </c>
       <c r="F10">
-        <v>909.5</v>
+        <v>902.5</v>
       </c>
       <c r="G10" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H10">
-        <v>15.5</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -2769,25 +3365,22 @@
         <v>하역내구</v>
       </c>
       <c r="D11" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E11">
-        <v>909.5</v>
+        <v>902.5</v>
       </c>
       <c r="F11">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="G11" t="str">
         <v>LPG</v>
       </c>
-      <c r="H11">
-        <v>21.2</v>
-      </c>
       <c r="I11" t="str">
-        <v>운전석 계기판 화면 깜빡임(예시)</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>IMG_20260714_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2801,19 +3394,16 @@
         <v>하역내구</v>
       </c>
       <c r="D12" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E12">
+        <v>909</v>
+      </c>
+      <c r="F12">
         <v>916</v>
-      </c>
-      <c r="F12">
-        <v>921</v>
       </c>
       <c r="G12" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H12">
-        <v>14.9</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -2833,19 +3423,19 @@
         <v>하역내구</v>
       </c>
       <c r="D13" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E13">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="F13">
-        <v>927.5</v>
+        <v>924</v>
       </c>
       <c r="G13" t="str">
         <v>LPG</v>
       </c>
       <c r="H13">
-        <v>20.7</v>
+        <v>73.1</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -2865,25 +3455,22 @@
         <v>하역내구</v>
       </c>
       <c r="D14" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E14">
-        <v>927.5</v>
+        <v>924</v>
       </c>
       <c r="F14">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="G14" t="str">
         <v>LPG</v>
       </c>
-      <c r="H14">
-        <v>17.2</v>
-      </c>
       <c r="I14" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>IMG_20260717_2(예시).jpg</v>
       </c>
     </row>
     <row r="15">
@@ -2897,19 +3484,19 @@
         <v>하역내구</v>
       </c>
       <c r="D15" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E15">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F15">
-        <v>938.5</v>
+        <v>937</v>
       </c>
       <c r="G15" t="str">
         <v>LPG</v>
       </c>
       <c r="H15">
-        <v>17.3</v>
+        <v>55.1</v>
       </c>
       <c r="I15" t="str">
         <v>작동유 온도 경고등 점등 후 소등(예시)</v>
@@ -2929,19 +3516,16 @@
         <v>하역내구</v>
       </c>
       <c r="D16" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E16">
-        <v>938.5</v>
+        <v>937</v>
       </c>
       <c r="F16">
-        <v>944.5</v>
+        <v>943.5</v>
       </c>
       <c r="G16" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H16">
-        <v>19.2</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -2961,19 +3545,16 @@
         <v>하역내구</v>
       </c>
       <c r="D17" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E17">
-        <v>944.5</v>
+        <v>943.5</v>
       </c>
       <c r="F17">
-        <v>950</v>
+        <v>948.5</v>
       </c>
       <c r="G17" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H17">
-        <v>16.7</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -2993,25 +3574,25 @@
         <v>하역내구</v>
       </c>
       <c r="D18" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E18">
-        <v>950</v>
+        <v>948.5</v>
       </c>
       <c r="F18">
-        <v>957.5</v>
+        <v>956</v>
       </c>
       <c r="G18" t="str">
         <v>LPG</v>
       </c>
       <c r="H18">
-        <v>21.5</v>
+        <v>70.9</v>
       </c>
       <c r="I18" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v>IMG_20260723_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -3025,25 +3606,22 @@
         <v>하역내구</v>
       </c>
       <c r="D19" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E19">
-        <v>957.5</v>
+        <v>956</v>
       </c>
       <c r="F19">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G19" t="str">
         <v>LPG</v>
       </c>
-      <c r="H19">
-        <v>15.7</v>
-      </c>
       <c r="I19" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J19" t="str">
-        <v>IMG_20260724_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -3057,19 +3635,19 @@
         <v>하역내구</v>
       </c>
       <c r="D20" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E20">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F20">
-        <v>970</v>
+        <v>970.5</v>
       </c>
       <c r="G20" t="str">
         <v>LPG</v>
       </c>
       <c r="H20">
-        <v>21.6</v>
+        <v>55.3</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -3089,19 +3667,16 @@
         <v>하역내구</v>
       </c>
       <c r="D21" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E21">
-        <v>970</v>
+        <v>970.5</v>
       </c>
       <c r="F21">
-        <v>975.5</v>
+        <v>977.5</v>
       </c>
       <c r="G21" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H21">
-        <v>17.3</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -3121,19 +3696,16 @@
         <v>하역내구</v>
       </c>
       <c r="D22" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E22">
-        <v>975.5</v>
+        <v>977.5</v>
       </c>
       <c r="F22">
-        <v>981.5</v>
+        <v>984.5</v>
       </c>
       <c r="G22" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H22">
-        <v>20.1</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -3153,25 +3725,25 @@
         <v>하역내구</v>
       </c>
       <c r="D23" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E23">
-        <v>981.5</v>
+        <v>984.5</v>
       </c>
       <c r="F23">
-        <v>988.5</v>
+        <v>991</v>
       </c>
       <c r="G23" t="str">
         <v>LPG</v>
       </c>
       <c r="H23">
-        <v>21.3</v>
+        <v>60.5</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>IMG_20260730_2(예시).jpg</v>
       </c>
     </row>
     <row r="24">
@@ -3185,19 +3757,19 @@
         <v>하역내구</v>
       </c>
       <c r="D24" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E24">
-        <v>988.5</v>
+        <v>991</v>
       </c>
       <c r="F24">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="G24" t="str">
         <v>LPG</v>
       </c>
       <c r="H24">
-        <v>17.4</v>
+        <v>80.2</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -3217,19 +3789,16 @@
         <v>하역내구</v>
       </c>
       <c r="D25" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E25">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="F25">
-        <v>999</v>
+        <v>1004.5</v>
       </c>
       <c r="G25" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H25">
-        <v>15.8</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -3249,19 +3818,16 @@
         <v>하역내구</v>
       </c>
       <c r="D26" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E26">
-        <v>999</v>
+        <v>1004.5</v>
       </c>
       <c r="F26">
-        <v>1005</v>
+        <v>1009.5</v>
       </c>
       <c r="G26" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H26">
-        <v>19.3</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -3281,25 +3847,25 @@
         <v>하역내구</v>
       </c>
       <c r="D27" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E27">
-        <v>1005</v>
+        <v>1009.5</v>
       </c>
       <c r="F27">
-        <v>1010.5</v>
+        <v>1015.5</v>
       </c>
       <c r="G27" t="str">
         <v>LPG</v>
       </c>
       <c r="H27">
-        <v>16.1</v>
+        <v>51.8</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>IMG_20260806_2(예시).jpg</v>
       </c>
     </row>
     <row r="28">
@@ -3313,19 +3879,16 @@
         <v>하역내구</v>
       </c>
       <c r="D28" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E28">
-        <v>1010.5</v>
+        <v>1015.5</v>
       </c>
       <c r="F28">
-        <v>1015.5</v>
+        <v>1020.5</v>
       </c>
       <c r="G28" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H28">
-        <v>15.8</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -3345,19 +3908,19 @@
         <v>하역내구</v>
       </c>
       <c r="D29" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E29">
-        <v>1015.5</v>
+        <v>1020.5</v>
       </c>
       <c r="F29">
-        <v>1020.5</v>
+        <v>1025.5</v>
       </c>
       <c r="G29" t="str">
         <v>LPG</v>
       </c>
       <c r="H29">
-        <v>15.7</v>
+        <v>50.9</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -3377,19 +3940,16 @@
         <v>하역내구</v>
       </c>
       <c r="D30" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E30">
-        <v>1020.5</v>
+        <v>1025.5</v>
       </c>
       <c r="F30">
-        <v>1028.5</v>
+        <v>1033</v>
       </c>
       <c r="G30" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H30">
-        <v>23.2</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -3409,25 +3969,22 @@
         <v>하역내구</v>
       </c>
       <c r="D31" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E31">
-        <v>1028.5</v>
+        <v>1033</v>
       </c>
       <c r="F31">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="G31" t="str">
         <v>LPG</v>
       </c>
-      <c r="H31">
-        <v>18.5</v>
-      </c>
       <c r="I31" t="str">
-        <v/>
+        <v>충전 커넥터 체결 불량(예시)</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>IMG_20260812_2(예시).jpg</v>
       </c>
     </row>
     <row r="32">
@@ -3441,19 +3998,19 @@
         <v>하역내구</v>
       </c>
       <c r="D32" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E32">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="F32">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="G32" t="str">
         <v>LPG</v>
       </c>
       <c r="H32">
-        <v>19.8</v>
+        <v>74.6</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -3473,19 +4030,16 @@
         <v>하역내구</v>
       </c>
       <c r="D33" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E33">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="F33">
-        <v>1047</v>
+        <v>1052.5</v>
       </c>
       <c r="G33" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H33">
-        <v>18.3</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -3505,25 +4059,25 @@
         <v>하역내구</v>
       </c>
       <c r="D34" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E34">
-        <v>1047</v>
+        <v>1052.5</v>
       </c>
       <c r="F34">
-        <v>1053.5</v>
+        <v>1057.5</v>
       </c>
       <c r="G34" t="str">
         <v>LPG</v>
       </c>
       <c r="H34">
-        <v>20.1</v>
+        <v>47.4</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>IMG_20260817_2(예시).jpg</v>
       </c>
     </row>
     <row r="35">
@@ -3537,25 +4091,22 @@
         <v>하역내구</v>
       </c>
       <c r="D35" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E35">
-        <v>1053.5</v>
+        <v>1057.5</v>
       </c>
       <c r="F35">
-        <v>1058.5</v>
+        <v>1062.5</v>
       </c>
       <c r="G35" t="str">
         <v>LPG</v>
       </c>
-      <c r="H35">
-        <v>14.9</v>
-      </c>
       <c r="I35" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J35" t="str">
-        <v>IMG_20260818_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -3569,19 +4120,16 @@
         <v>하역내구</v>
       </c>
       <c r="D36" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E36">
-        <v>1058.5</v>
+        <v>1062.5</v>
       </c>
       <c r="F36">
-        <v>1064.5</v>
+        <v>1067.5</v>
       </c>
       <c r="G36" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H36">
-        <v>17</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -3601,19 +4149,19 @@
         <v>하역내구</v>
       </c>
       <c r="D37" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E37">
-        <v>1064.5</v>
+        <v>1067.5</v>
       </c>
       <c r="F37">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="G37" t="str">
         <v>LPG</v>
       </c>
       <c r="H37">
-        <v>16.3</v>
+        <v>54</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -3633,19 +4181,16 @@
         <v>하역내구</v>
       </c>
       <c r="D38" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E38">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F38">
-        <v>1078</v>
+        <v>1078.5</v>
       </c>
       <c r="G38" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H38">
-        <v>22.7</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -3665,25 +4210,25 @@
         <v>하역내구</v>
       </c>
       <c r="D39" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E39">
-        <v>1078</v>
+        <v>1078.5</v>
       </c>
       <c r="F39">
-        <v>1084</v>
+        <v>1085.5</v>
       </c>
       <c r="G39" t="str">
         <v>LPG</v>
       </c>
       <c r="H39">
-        <v>19.8</v>
+        <v>64.2</v>
       </c>
       <c r="I39" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J39" t="str">
-        <v>IMG_20260824_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -3697,19 +4242,16 @@
         <v>하역내구</v>
       </c>
       <c r="D40" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E40">
-        <v>1084</v>
+        <v>1085.5</v>
       </c>
       <c r="F40">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="G40" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H40">
-        <v>16.2</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -3729,25 +4271,22 @@
         <v>하역내구</v>
       </c>
       <c r="D41" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E41">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="F41">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="G41" t="str">
         <v>LPG</v>
       </c>
-      <c r="H41">
-        <v>18.4</v>
-      </c>
       <c r="I41" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J41" t="str">
-        <v>IMG_20260826_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -3761,19 +4300,19 @@
         <v>하역내구</v>
       </c>
       <c r="D42" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E42">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="F42">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="G42" t="str">
         <v>LPG</v>
       </c>
       <c r="H42">
-        <v>24.5</v>
+        <v>77</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -3793,19 +4332,16 @@
         <v>하역내구</v>
       </c>
       <c r="D43" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E43">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="F43">
-        <v>1110.5</v>
+        <v>1115</v>
       </c>
       <c r="G43" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H43">
-        <v>21.3</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -3825,19 +4361,19 @@
         <v>하역내구</v>
       </c>
       <c r="D44" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E44">
-        <v>1110.5</v>
+        <v>1115</v>
       </c>
       <c r="F44">
-        <v>1115.5</v>
+        <v>1122</v>
       </c>
       <c r="G44" t="str">
         <v>LPG</v>
       </c>
       <c r="H44">
-        <v>16.4</v>
+        <v>67.3</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -3857,19 +4393,16 @@
         <v>하역내구</v>
       </c>
       <c r="D45" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E45">
-        <v>1115.5</v>
+        <v>1122</v>
       </c>
       <c r="F45">
-        <v>1120.5</v>
+        <v>1127</v>
       </c>
       <c r="G45" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H45">
-        <v>15.2</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -3889,19 +4422,16 @@
         <v>하역내구</v>
       </c>
       <c r="D46" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E46">
-        <v>1120.5</v>
+        <v>1127</v>
       </c>
       <c r="F46">
-        <v>1127.5</v>
+        <v>1132</v>
       </c>
       <c r="G46" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H46">
-        <v>22.4</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -3921,19 +4451,19 @@
         <v>하역내구</v>
       </c>
       <c r="D47" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E47">
-        <v>1127.5</v>
+        <v>1132</v>
       </c>
       <c r="F47">
-        <v>1132.5</v>
+        <v>1138</v>
       </c>
       <c r="G47" t="str">
         <v>LPG</v>
       </c>
       <c r="H47">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -3953,19 +4483,16 @@
         <v>하역내구</v>
       </c>
       <c r="D48" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E48">
-        <v>1132.5</v>
+        <v>1138</v>
       </c>
       <c r="F48">
-        <v>1139.5</v>
+        <v>1144.5</v>
       </c>
       <c r="G48" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H48">
-        <v>20.1</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -3985,19 +4512,19 @@
         <v>하역내구</v>
       </c>
       <c r="D49" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E49">
-        <v>1139.5</v>
+        <v>1144.5</v>
       </c>
       <c r="F49">
-        <v>1146.5</v>
+        <v>1152</v>
       </c>
       <c r="G49" t="str">
         <v>LPG</v>
       </c>
       <c r="H49">
-        <v>23</v>
+        <v>68.1</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -4017,25 +4544,22 @@
         <v>하역내구</v>
       </c>
       <c r="D50" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E50">
-        <v>1146.5</v>
+        <v>1152</v>
       </c>
       <c r="F50">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="G50" t="str">
         <v>LPG</v>
       </c>
-      <c r="H50">
-        <v>20.2</v>
-      </c>
       <c r="I50" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v/>
       </c>
       <c r="J50" t="str">
-        <v>IMG_20260908_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -4049,19 +4573,16 @@
         <v>하역내구</v>
       </c>
       <c r="D51" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E51">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="F51">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="G51" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H51">
-        <v>16.7</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -4081,19 +4602,19 @@
         <v>하역내구</v>
       </c>
       <c r="D52" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E52">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="F52">
-        <v>1166</v>
+        <v>1175.5</v>
       </c>
       <c r="G52" t="str">
         <v>LPG</v>
       </c>
       <c r="H52">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -4113,25 +4634,22 @@
         <v>하역내구</v>
       </c>
       <c r="D53" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E53">
-        <v>1166</v>
+        <v>1175.5</v>
       </c>
       <c r="F53">
-        <v>1172.5</v>
+        <v>1183.5</v>
       </c>
       <c r="G53" t="str">
         <v>LPG</v>
       </c>
-      <c r="H53">
-        <v>20.2</v>
-      </c>
       <c r="I53" t="str">
-        <v>운전석 계기판 화면 깜빡임(예시)</v>
+        <v/>
       </c>
       <c r="J53" t="str">
-        <v>IMG_20260911_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -4145,19 +4663,19 @@
         <v>하역내구</v>
       </c>
       <c r="D54" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E54">
-        <v>1172.5</v>
+        <v>1183.5</v>
       </c>
       <c r="F54">
-        <v>1180</v>
+        <v>1191</v>
       </c>
       <c r="G54" t="str">
         <v>LPG</v>
       </c>
       <c r="H54">
-        <v>22.8</v>
+        <v>65.6</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -4177,19 +4695,16 @@
         <v>하역내구</v>
       </c>
       <c r="D55" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E55">
-        <v>1180</v>
+        <v>1191</v>
       </c>
       <c r="F55">
-        <v>1185</v>
+        <v>1196.5</v>
       </c>
       <c r="G55" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H55">
-        <v>15.6</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -4209,19 +4724,16 @@
         <v>하역내구</v>
       </c>
       <c r="D56" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E56">
-        <v>1185</v>
+        <v>1196.5</v>
       </c>
       <c r="F56">
-        <v>1190</v>
+        <v>1202.5</v>
       </c>
       <c r="G56" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H56">
-        <v>14.8</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -4241,19 +4753,19 @@
         <v>하역내구</v>
       </c>
       <c r="D57" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E57">
-        <v>1190</v>
+        <v>1202.5</v>
       </c>
       <c r="F57">
-        <v>1195</v>
+        <v>1209</v>
       </c>
       <c r="G57" t="str">
         <v>LPG</v>
       </c>
       <c r="H57">
-        <v>17</v>
+        <v>55.5</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -4273,19 +4785,16 @@
         <v>하역내구</v>
       </c>
       <c r="D58" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E58">
-        <v>1195</v>
+        <v>1209</v>
       </c>
       <c r="F58">
-        <v>1202</v>
+        <v>1215.5</v>
       </c>
       <c r="G58" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H58">
-        <v>22.9</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -4305,25 +4814,25 @@
         <v>하역내구</v>
       </c>
       <c r="D59" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E59">
-        <v>1202</v>
+        <v>1215.5</v>
       </c>
       <c r="F59">
-        <v>1209</v>
+        <v>1221.5</v>
       </c>
       <c r="G59" t="str">
         <v>LPG</v>
       </c>
       <c r="H59">
-        <v>21.2</v>
+        <v>58.5</v>
       </c>
       <c r="I59" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
       <c r="J59" t="str">
-        <v>IMG_20260921_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -4337,19 +4846,16 @@
         <v>하역내구</v>
       </c>
       <c r="D60" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E60">
-        <v>1209</v>
+        <v>1221.5</v>
       </c>
       <c r="F60">
-        <v>1217</v>
+        <v>1228.5</v>
       </c>
       <c r="G60" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H60">
-        <v>26.8</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -4369,19 +4875,16 @@
         <v>하역내구</v>
       </c>
       <c r="D61" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E61">
-        <v>1217</v>
+        <v>1228.5</v>
       </c>
       <c r="F61">
-        <v>1225</v>
+        <v>1236</v>
       </c>
       <c r="G61" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H61">
-        <v>23.3</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -4401,22 +4904,22 @@
         <v>하역내구</v>
       </c>
       <c r="D62" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E62">
-        <v>1225</v>
+        <v>1236</v>
       </c>
       <c r="F62">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="G62" t="str">
         <v>LPG</v>
       </c>
       <c r="H62">
-        <v>24.7</v>
+        <v>42.8</v>
       </c>
       <c r="I62" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
       <c r="J62" t="str">
         <v>IMG_20260924_2(예시).jpg</v>
@@ -4433,19 +4936,16 @@
         <v>하역내구</v>
       </c>
       <c r="D63" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E63">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="F63">
-        <v>1238</v>
+        <v>1246.5</v>
       </c>
       <c r="G63" t="str">
         <v>LPG</v>
-      </c>
-      <c r="H63">
-        <v>15.8</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -4513,25 +5013,25 @@
         <v>주행내구</v>
       </c>
       <c r="D3" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E3">
         <v>432</v>
       </c>
       <c r="F3">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H3">
-        <v>24</v>
+        <v>27.8</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>IMG_20260701_3(예시).jpg</v>
       </c>
     </row>
     <row r="4">
@@ -4545,19 +5045,19 @@
         <v>주행내구</v>
       </c>
       <c r="D4" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E4">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F4">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G4">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H4">
-        <v>20.2</v>
+        <v>23.4</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -4577,19 +5077,19 @@
         <v>주행내구</v>
       </c>
       <c r="D5" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E5">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F5">
-        <v>447.5</v>
+        <v>451.5</v>
       </c>
       <c r="G5">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H5">
-        <v>26.2</v>
+        <v>21.8</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -4609,19 +5109,19 @@
         <v>주행내구</v>
       </c>
       <c r="D6" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E6">
-        <v>447.5</v>
+        <v>451.5</v>
       </c>
       <c r="F6">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G6">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H6">
-        <v>19.8</v>
+        <v>22.1</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -4641,19 +5141,19 @@
         <v>주행내구</v>
       </c>
       <c r="D7" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E7">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F7">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G7">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="H7">
-        <v>25.3</v>
+        <v>18.9</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -4673,19 +5173,19 @@
         <v>주행내구</v>
       </c>
       <c r="D8" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E8">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F8">
-        <v>469.5</v>
+        <v>469</v>
       </c>
       <c r="G8">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H8">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -4705,19 +5205,19 @@
         <v>주행내구</v>
       </c>
       <c r="D9" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E9">
-        <v>469.5</v>
+        <v>469</v>
       </c>
       <c r="F9">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G9">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -4737,19 +5237,19 @@
         <v>주행내구</v>
       </c>
       <c r="D10" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E10">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F10">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G10">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H10">
-        <v>28.8</v>
+        <v>23.7</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -4769,19 +5269,19 @@
         <v>주행내구</v>
       </c>
       <c r="D11" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E11">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F11">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G11">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -4801,19 +5301,19 @@
         <v>주행내구</v>
       </c>
       <c r="D12" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E12">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F12">
-        <v>498</v>
+        <v>496.5</v>
       </c>
       <c r="G12">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="H12">
-        <v>19.8</v>
+        <v>23.4</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -4836,16 +5336,16 @@
         <v/>
       </c>
       <c r="E13">
-        <v>498</v>
+        <v>496.5</v>
       </c>
       <c r="F13">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G13">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H13">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -4865,19 +5365,19 @@
         <v>주행내구</v>
       </c>
       <c r="D14" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E14">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F14">
-        <v>512.5</v>
+        <v>510</v>
       </c>
       <c r="G14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H14">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -4897,19 +5397,19 @@
         <v>주행내구</v>
       </c>
       <c r="D15" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E15">
-        <v>512.5</v>
+        <v>510</v>
       </c>
       <c r="F15">
-        <v>520</v>
+        <v>516.5</v>
       </c>
       <c r="G15">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="H15">
-        <v>18.6</v>
+        <v>24.6</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -4929,13 +5429,13 @@
         <v>주행내구</v>
       </c>
       <c r="D16" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E16">
-        <v>520</v>
+        <v>516.5</v>
       </c>
       <c r="F16">
-        <v>528</v>
+        <v>524.5</v>
       </c>
       <c r="G16">
         <v>67</v>
@@ -4961,19 +5461,19 @@
         <v>주행내구</v>
       </c>
       <c r="D17" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E17">
-        <v>528</v>
+        <v>524.5</v>
       </c>
       <c r="F17">
-        <v>535.5</v>
+        <v>532</v>
       </c>
       <c r="G17">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="H17">
-        <v>27.5</v>
+        <v>22.7</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -4993,19 +5493,19 @@
         <v>주행내구</v>
       </c>
       <c r="D18" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E18">
-        <v>535.5</v>
+        <v>532</v>
       </c>
       <c r="F18">
-        <v>543</v>
+        <v>539.5</v>
       </c>
       <c r="G18">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H18">
-        <v>22.4</v>
+        <v>26.6</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -5025,19 +5525,19 @@
         <v>주행내구</v>
       </c>
       <c r="D19" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E19">
-        <v>543</v>
+        <v>539.5</v>
       </c>
       <c r="F19">
-        <v>549</v>
+        <v>547.5</v>
       </c>
       <c r="G19">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="H19">
-        <v>20.2</v>
+        <v>26.2</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -5057,19 +5557,19 @@
         <v>주행내구</v>
       </c>
       <c r="D20" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E20">
-        <v>549</v>
+        <v>547.5</v>
       </c>
       <c r="F20">
-        <v>557</v>
+        <v>554.5</v>
       </c>
       <c r="G20">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H20">
-        <v>21.1</v>
+        <v>25</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -5089,19 +5589,19 @@
         <v>주행내구</v>
       </c>
       <c r="D21" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E21">
-        <v>557</v>
+        <v>554.5</v>
       </c>
       <c r="F21">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G21">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H21">
-        <v>24</v>
+        <v>28.8</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -5121,19 +5621,19 @@
         <v>주행내구</v>
       </c>
       <c r="D22" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E22">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F22">
-        <v>572.5</v>
+        <v>567.5</v>
       </c>
       <c r="G22">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="H22">
-        <v>21.1</v>
+        <v>28.5</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -5153,19 +5653,19 @@
         <v>주행내구</v>
       </c>
       <c r="D23" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E23">
-        <v>572.5</v>
+        <v>567.5</v>
       </c>
       <c r="F23">
-        <v>577.5</v>
+        <v>573.5</v>
       </c>
       <c r="G23">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="H23">
-        <v>27.8</v>
+        <v>23.7</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -5185,19 +5685,19 @@
         <v>주행내구</v>
       </c>
       <c r="D24" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E24">
-        <v>577.5</v>
+        <v>573.5</v>
       </c>
       <c r="F24">
-        <v>584.5</v>
+        <v>581</v>
       </c>
       <c r="G24">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="H24">
-        <v>26.9</v>
+        <v>18.6</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -5217,19 +5717,19 @@
         <v>주행내구</v>
       </c>
       <c r="D25" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E25">
-        <v>584.5</v>
+        <v>581</v>
       </c>
       <c r="F25">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G25">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H25">
-        <v>23</v>
+        <v>26.2</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -5249,19 +5749,19 @@
         <v>주행내구</v>
       </c>
       <c r="D26" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E26">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F26">
-        <v>596.5</v>
+        <v>593.5</v>
       </c>
       <c r="G26">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="H26">
-        <v>20.5</v>
+        <v>25.6</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -5281,25 +5781,25 @@
         <v>주행내구</v>
       </c>
       <c r="D27" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E27">
-        <v>596.5</v>
+        <v>593.5</v>
       </c>
       <c r="F27">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G27">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H27">
-        <v>24</v>
+        <v>26.9</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>IMG_20260804_3(예시).jpg</v>
       </c>
     </row>
     <row r="28">
@@ -5313,19 +5813,19 @@
         <v>주행내구</v>
       </c>
       <c r="D28" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E28">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F28">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G28">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="H28">
-        <v>24.3</v>
+        <v>19.8</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -5345,19 +5845,19 @@
         <v>주행내구</v>
       </c>
       <c r="D29" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E29">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F29">
         <v>614.5</v>
       </c>
       <c r="G29">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="H29">
-        <v>27.8</v>
+        <v>17.9</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -5377,19 +5877,19 @@
         <v>주행내구</v>
       </c>
       <c r="D30" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E30">
         <v>614.5</v>
       </c>
       <c r="F30">
-        <v>620.5</v>
+        <v>621.5</v>
       </c>
       <c r="G30">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="H30">
-        <v>25.9</v>
+        <v>21.1</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -5409,13 +5909,13 @@
         <v>주행내구</v>
       </c>
       <c r="D31" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E31">
-        <v>620.5</v>
+        <v>621.5</v>
       </c>
       <c r="F31">
-        <v>625.5</v>
+        <v>629.5</v>
       </c>
       <c r="G31">
         <v>77</v>
@@ -5441,19 +5941,19 @@
         <v>주행내구</v>
       </c>
       <c r="D32" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E32">
-        <v>625.5</v>
+        <v>629.5</v>
       </c>
       <c r="F32">
-        <v>631</v>
+        <v>636.5</v>
       </c>
       <c r="G32">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H32">
-        <v>25.6</v>
+        <v>18.9</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -5473,25 +5973,25 @@
         <v>주행내구</v>
       </c>
       <c r="D33" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E33">
-        <v>631</v>
+        <v>636.5</v>
       </c>
       <c r="F33">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="G33">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H33">
-        <v>17.9</v>
+        <v>19.2</v>
       </c>
       <c r="I33" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J33" t="str">
-        <v>IMG_20260812_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -5505,19 +6005,19 @@
         <v>주행내구</v>
       </c>
       <c r="D34" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E34">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F34">
-        <v>643.5</v>
+        <v>648.5</v>
       </c>
       <c r="G34">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H34">
-        <v>24.3</v>
+        <v>27.2</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -5537,19 +6037,19 @@
         <v>주행내구</v>
       </c>
       <c r="D35" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E35">
-        <v>643.5</v>
+        <v>648.5</v>
       </c>
       <c r="F35">
-        <v>648.5</v>
+        <v>653.5</v>
       </c>
       <c r="G35">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H35">
-        <v>20.8</v>
+        <v>19.8</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -5569,19 +6069,19 @@
         <v>주행내구</v>
       </c>
       <c r="D36" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E36">
-        <v>648.5</v>
+        <v>653.5</v>
       </c>
       <c r="F36">
-        <v>656.5</v>
+        <v>659</v>
       </c>
       <c r="G36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H36">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -5601,19 +6101,19 @@
         <v>주행내구</v>
       </c>
       <c r="D37" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E37">
-        <v>656.5</v>
+        <v>659</v>
       </c>
       <c r="F37">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G37">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H37">
-        <v>21.1</v>
+        <v>23.4</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -5633,25 +6133,25 @@
         <v>주행내구</v>
       </c>
       <c r="D38" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E38">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F38">
-        <v>669.5</v>
+        <v>671.5</v>
       </c>
       <c r="G38">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="H38">
-        <v>20.2</v>
+        <v>25.9</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>충전 커넥터 체결 불량(예시)</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>IMG_20260819_3(예시).jpg</v>
       </c>
     </row>
     <row r="39">
@@ -5665,19 +6165,19 @@
         <v>주행내구</v>
       </c>
       <c r="D39" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E39">
-        <v>669.5</v>
+        <v>671.5</v>
       </c>
       <c r="F39">
-        <v>675.5</v>
+        <v>677.5</v>
       </c>
       <c r="G39">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="H39">
-        <v>21.8</v>
+        <v>25.9</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -5697,19 +6197,19 @@
         <v>주행내구</v>
       </c>
       <c r="D40" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E40">
-        <v>675.5</v>
+        <v>677.5</v>
       </c>
       <c r="F40">
-        <v>682</v>
+        <v>685.5</v>
       </c>
       <c r="G40">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H40">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -5729,25 +6229,25 @@
         <v>주행내구</v>
       </c>
       <c r="D41" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E41">
-        <v>682</v>
+        <v>685.5</v>
       </c>
       <c r="F41">
-        <v>688.5</v>
+        <v>693</v>
       </c>
       <c r="G41">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H41">
-        <v>18.2</v>
+        <v>21.1</v>
       </c>
       <c r="I41" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J41" t="str">
-        <v>IMG_20260824_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -5761,19 +6261,19 @@
         <v>주행내구</v>
       </c>
       <c r="D42" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E42">
-        <v>688.5</v>
+        <v>693</v>
       </c>
       <c r="F42">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G42">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H42">
-        <v>21.1</v>
+        <v>19.2</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -5793,19 +6293,19 @@
         <v>주행내구</v>
       </c>
       <c r="D43" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E43">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="F43">
-        <v>701.5</v>
+        <v>706</v>
       </c>
       <c r="G43">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H43">
-        <v>27.2</v>
+        <v>28.5</v>
       </c>
       <c r="I43" t="str">
         <v>운전석 계기판 화면 깜빡임(예시)</v>
@@ -5825,19 +6325,19 @@
         <v>주행내구</v>
       </c>
       <c r="D44" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E44">
-        <v>701.5</v>
+        <v>706</v>
       </c>
       <c r="F44">
-        <v>708.5</v>
+        <v>711.5</v>
       </c>
       <c r="G44">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H44">
-        <v>17.9</v>
+        <v>22.1</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -5857,25 +6357,25 @@
         <v>주행내구</v>
       </c>
       <c r="D45" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E45">
-        <v>708.5</v>
+        <v>711.5</v>
       </c>
       <c r="F45">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G45">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H45">
-        <v>23.7</v>
+        <v>21.1</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>IMG_20260828_3(예시).jpg</v>
       </c>
     </row>
     <row r="46">
@@ -5889,13 +6389,13 @@
         <v>주행내구</v>
       </c>
       <c r="D46" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E46">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F46">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="G46">
         <v>78</v>
@@ -5921,25 +6421,25 @@
         <v>주행내구</v>
       </c>
       <c r="D47" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E47">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F47">
-        <v>728.5</v>
+        <v>733</v>
       </c>
       <c r="G47">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H47">
-        <v>26.6</v>
+        <v>28.2</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>IMG_20260901_3(예시).jpg</v>
       </c>
     </row>
     <row r="48">
@@ -5953,19 +6453,19 @@
         <v>주행내구</v>
       </c>
       <c r="D48" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E48">
-        <v>728.5</v>
+        <v>733</v>
       </c>
       <c r="F48">
-        <v>735</v>
+        <v>738.5</v>
       </c>
       <c r="G48">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H48">
-        <v>22.7</v>
+        <v>20.8</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -5985,19 +6485,19 @@
         <v>주행내구</v>
       </c>
       <c r="D49" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E49">
-        <v>735</v>
+        <v>738.5</v>
       </c>
       <c r="F49">
-        <v>742.5</v>
+        <v>744.5</v>
       </c>
       <c r="G49">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H49">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -6017,19 +6517,19 @@
         <v>주행내구</v>
       </c>
       <c r="D50" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E50">
-        <v>742.5</v>
+        <v>744.5</v>
       </c>
       <c r="F50">
-        <v>749.5</v>
+        <v>752</v>
       </c>
       <c r="G50">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="H50">
-        <v>19.2</v>
+        <v>28.5</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -6049,19 +6549,19 @@
         <v>주행내구</v>
       </c>
       <c r="D51" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E51">
-        <v>749.5</v>
+        <v>752</v>
       </c>
       <c r="F51">
-        <v>757.5</v>
+        <v>758.5</v>
       </c>
       <c r="G51">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="H51">
-        <v>23</v>
+        <v>27.8</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -6081,19 +6581,19 @@
         <v>주행내구</v>
       </c>
       <c r="D52" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E52">
-        <v>757.5</v>
+        <v>758.5</v>
       </c>
       <c r="F52">
-        <v>765.5</v>
+        <v>764.5</v>
       </c>
       <c r="G52">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="H52">
-        <v>18.6</v>
+        <v>23.7</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -6113,19 +6613,19 @@
         <v>주행내구</v>
       </c>
       <c r="D53" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E53">
-        <v>765.5</v>
+        <v>764.5</v>
       </c>
       <c r="F53">
         <v>771.5</v>
       </c>
       <c r="G53">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H53">
-        <v>28.5</v>
+        <v>18.9</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -6145,19 +6645,19 @@
         <v>주행내구</v>
       </c>
       <c r="D54" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자C</v>
       </c>
       <c r="E54">
         <v>771.5</v>
       </c>
       <c r="F54">
-        <v>779</v>
+        <v>778.5</v>
       </c>
       <c r="G54">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H54">
-        <v>22.7</v>
+        <v>28.2</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -6177,19 +6677,19 @@
         <v>주행내구</v>
       </c>
       <c r="D55" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자D</v>
       </c>
       <c r="E55">
-        <v>779</v>
+        <v>778.5</v>
       </c>
       <c r="F55">
-        <v>785.5</v>
+        <v>786.5</v>
       </c>
       <c r="G55">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H55">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -6209,19 +6709,19 @@
         <v>주행내구</v>
       </c>
       <c r="D56" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자A</v>
       </c>
       <c r="E56">
-        <v>785.5</v>
+        <v>786.5</v>
       </c>
       <c r="F56">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G56">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="H56">
-        <v>23.4</v>
+        <v>19.5</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -6241,19 +6741,19 @@
         <v>주행내구</v>
       </c>
       <c r="D57" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자B</v>
       </c>
       <c r="E57">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F57">
-        <v>799.5</v>
+        <v>798.5</v>
       </c>
       <c r="G57">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H57">
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -6273,19 +6773,19 @@
         <v>주행내구</v>
       </c>
       <c r="D58" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자C</v>
       </c>
       <c r="E58">
-        <v>799.5</v>
+        <v>798.5</v>
       </c>
       <c r="F58">
-        <v>806.5</v>
+        <v>804.5</v>
       </c>
       <c r="G58">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H58">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -6305,19 +6805,19 @@
         <v>주행내구</v>
       </c>
       <c r="D59" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자D</v>
       </c>
       <c r="E59">
-        <v>806.5</v>
+        <v>804.5</v>
       </c>
       <c r="F59">
-        <v>811.5</v>
+        <v>810</v>
       </c>
       <c r="G59">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="H59">
-        <v>22.7</v>
+        <v>19.2</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -6337,19 +6837,19 @@
         <v>주행내구</v>
       </c>
       <c r="D60" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자A</v>
       </c>
       <c r="E60">
-        <v>811.5</v>
+        <v>810</v>
       </c>
       <c r="F60">
-        <v>819</v>
+        <v>816.5</v>
       </c>
       <c r="G60">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H60">
-        <v>22.1</v>
+        <v>28.2</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -6369,19 +6869,19 @@
         <v>주행내구</v>
       </c>
       <c r="D61" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자B</v>
       </c>
       <c r="E61">
-        <v>819</v>
+        <v>816.5</v>
       </c>
       <c r="F61">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="G61">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H61">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -6401,19 +6901,19 @@
         <v>주행내구</v>
       </c>
       <c r="D62" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자C</v>
       </c>
       <c r="E62">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="F62">
-        <v>833</v>
+        <v>830.5</v>
       </c>
       <c r="G62">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H62">
-        <v>23.7</v>
+        <v>28.8</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -6433,25 +6933,25 @@
         <v>주행내구</v>
       </c>
       <c r="D63" t="str">
-        <v>예시 운전자A</v>
+        <v>운전자D</v>
       </c>
       <c r="E63">
-        <v>833</v>
+        <v>830.5</v>
       </c>
       <c r="F63">
-        <v>840.5</v>
+        <v>835.5</v>
       </c>
       <c r="G63">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="H63">
-        <v>25.9</v>
+        <v>18.6</v>
       </c>
       <c r="I63" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J63" t="str">
-        <v>IMG_20260923_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -6465,19 +6965,19 @@
         <v>주행내구</v>
       </c>
       <c r="D64" t="str">
-        <v>예시 운전자B</v>
+        <v>운전자A</v>
       </c>
       <c r="E64">
-        <v>840.5</v>
+        <v>835.5</v>
       </c>
       <c r="F64">
-        <v>846.5</v>
+        <v>841</v>
       </c>
       <c r="G64">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H64">
-        <v>21.1</v>
+        <v>26.2</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -6497,19 +6997,19 @@
         <v>주행내구</v>
       </c>
       <c r="D65" t="str">
-        <v>예시 운전자C</v>
+        <v>운전자B</v>
       </c>
       <c r="E65">
-        <v>846.5</v>
+        <v>841</v>
       </c>
       <c r="F65">
-        <v>852</v>
+        <v>847.5</v>
       </c>
       <c r="G65">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="H65">
-        <v>19.5</v>
+        <v>28.5</v>
       </c>
       <c r="I65" t="str">
         <v/>

--- a/samples/예시데이터_모델별엑셀.xlsx
+++ b/samples/예시데이터_모델별엑셀.xlsx
@@ -516,7 +516,7 @@
         <v>1253</v>
       </c>
       <c r="F5">
-        <v>1260.5</v>
+        <v>1258.5</v>
       </c>
       <c r="G5" t="str">
         <v>경유</v>
@@ -542,10 +542,10 @@
         <v>운전자D</v>
       </c>
       <c r="E6">
-        <v>1260.5</v>
+        <v>1258.5</v>
       </c>
       <c r="F6">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G6" t="str">
         <v>경유</v>
@@ -571,16 +571,16 @@
         <v>운전자A</v>
       </c>
       <c r="E7">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F7">
-        <v>1272.5</v>
+        <v>1272</v>
       </c>
       <c r="G7" t="str">
         <v>경유</v>
       </c>
       <c r="H7">
-        <v>45.5</v>
+        <v>48.3</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -603,10 +603,10 @@
         <v>운전자B</v>
       </c>
       <c r="E8">
-        <v>1272.5</v>
+        <v>1272</v>
       </c>
       <c r="F8">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="G8" t="str">
         <v>경유</v>
@@ -632,10 +632,10 @@
         <v>운전자D</v>
       </c>
       <c r="E9">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="F9">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="G9" t="str">
         <v>경유</v>
@@ -661,10 +661,10 @@
         <v>운전자C</v>
       </c>
       <c r="E10">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="F10">
-        <v>1292.5</v>
+        <v>1289.5</v>
       </c>
       <c r="G10" t="str">
         <v>경유</v>
@@ -690,16 +690,16 @@
         <v>운전자D</v>
       </c>
       <c r="E11">
-        <v>1292.5</v>
+        <v>1289.5</v>
       </c>
       <c r="F11">
-        <v>1300.5</v>
+        <v>1296</v>
       </c>
       <c r="G11" t="str">
         <v>경유</v>
       </c>
       <c r="H11">
-        <v>61.6</v>
+        <v>53.7</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -722,10 +722,10 @@
         <v>운전자B</v>
       </c>
       <c r="E12">
-        <v>1300.5</v>
+        <v>1296</v>
       </c>
       <c r="F12">
-        <v>1306.5</v>
+        <v>1304</v>
       </c>
       <c r="G12" t="str">
         <v>경유</v>
@@ -751,10 +751,10 @@
         <v>운전자A</v>
       </c>
       <c r="E13">
-        <v>1306.5</v>
+        <v>1304</v>
       </c>
       <c r="F13">
-        <v>1314.5</v>
+        <v>1311</v>
       </c>
       <c r="G13" t="str">
         <v>경유</v>
@@ -780,16 +780,16 @@
         <v>운전자B</v>
       </c>
       <c r="E14">
-        <v>1314.5</v>
+        <v>1311</v>
       </c>
       <c r="F14">
-        <v>1321.5</v>
+        <v>1318</v>
       </c>
       <c r="G14" t="str">
         <v>경유</v>
       </c>
       <c r="H14">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -812,10 +812,10 @@
         <v>운전자C</v>
       </c>
       <c r="E15">
-        <v>1321.5</v>
+        <v>1318</v>
       </c>
       <c r="F15">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="G15" t="str">
         <v>경유</v>
@@ -841,10 +841,10 @@
         <v>운전자A</v>
       </c>
       <c r="E16">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="F16">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G16" t="str">
         <v>경유</v>
@@ -870,10 +870,10 @@
         <v>운전자D</v>
       </c>
       <c r="E17">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F17">
-        <v>1340.5</v>
+        <v>1341.5</v>
       </c>
       <c r="G17" t="str">
         <v>경유</v>
@@ -899,22 +899,22 @@
         <v>운전자A</v>
       </c>
       <c r="E18">
-        <v>1340.5</v>
+        <v>1341.5</v>
       </c>
       <c r="F18">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="G18" t="str">
         <v>경유</v>
       </c>
       <c r="H18">
-        <v>48.8</v>
+        <v>56.7</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>IMG_20260716_1(예시).jpg</v>
       </c>
     </row>
     <row r="19">
@@ -931,10 +931,10 @@
         <v>운전자C</v>
       </c>
       <c r="E19">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="F19">
-        <v>1351.5</v>
+        <v>1354</v>
       </c>
       <c r="G19" t="str">
         <v>경유</v>
@@ -960,19 +960,19 @@
         <v>운전자B</v>
       </c>
       <c r="E20">
-        <v>1351.5</v>
+        <v>1354</v>
       </c>
       <c r="F20">
-        <v>1358.5</v>
+        <v>1361</v>
       </c>
       <c r="G20" t="str">
         <v>경유</v>
       </c>
       <c r="I20" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J20" t="str">
-        <v>IMG_20260717_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -989,16 +989,16 @@
         <v>운전자C</v>
       </c>
       <c r="E21">
-        <v>1358.5</v>
+        <v>1361</v>
       </c>
       <c r="F21">
-        <v>1364</v>
+        <v>1366.5</v>
       </c>
       <c r="G21" t="str">
         <v>경유</v>
       </c>
       <c r="H21">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1021,10 +1021,10 @@
         <v>운전자D</v>
       </c>
       <c r="E22">
-        <v>1352</v>
+        <v>1354.5</v>
       </c>
       <c r="F22">
-        <v>1358.5</v>
+        <v>1362</v>
       </c>
       <c r="G22" t="str">
         <v>경유</v>
@@ -1050,10 +1050,10 @@
         <v>운전자B</v>
       </c>
       <c r="E23">
-        <v>1358.5</v>
+        <v>1362</v>
       </c>
       <c r="F23">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="G23" t="str">
         <v>경유</v>
@@ -1079,10 +1079,10 @@
         <v>운전자A</v>
       </c>
       <c r="E24">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="F24">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="G24" t="str">
         <v>경유</v>
@@ -1108,16 +1108,16 @@
         <v>운전자B</v>
       </c>
       <c r="E25">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="F25">
-        <v>1377</v>
+        <v>1381.5</v>
       </c>
       <c r="G25" t="str">
         <v>경유</v>
       </c>
       <c r="H25">
-        <v>52.3</v>
+        <v>62.5</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1140,10 +1140,10 @@
         <v>운전자D</v>
       </c>
       <c r="E26">
-        <v>1377</v>
+        <v>1381.5</v>
       </c>
       <c r="F26">
-        <v>1383</v>
+        <v>1387.5</v>
       </c>
       <c r="G26" t="str">
         <v>경유</v>
@@ -1169,10 +1169,10 @@
         <v>운전자C</v>
       </c>
       <c r="E27">
-        <v>1383</v>
+        <v>1387.5</v>
       </c>
       <c r="F27">
-        <v>1390.5</v>
+        <v>1393</v>
       </c>
       <c r="G27" t="str">
         <v>경유</v>
@@ -1198,16 +1198,16 @@
         <v>운전자D</v>
       </c>
       <c r="E28">
-        <v>1390.5</v>
+        <v>1393</v>
       </c>
       <c r="F28">
-        <v>1398</v>
+        <v>1400.5</v>
       </c>
       <c r="G28" t="str">
         <v>경유</v>
       </c>
       <c r="H28">
-        <v>60.9</v>
+        <v>60.4</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1230,10 +1230,10 @@
         <v>운전자A</v>
       </c>
       <c r="E29">
-        <v>1398</v>
+        <v>1400.5</v>
       </c>
       <c r="F29">
-        <v>1403.5</v>
+        <v>1406</v>
       </c>
       <c r="G29" t="str">
         <v>경유</v>
@@ -1259,10 +1259,10 @@
         <v>운전자C</v>
       </c>
       <c r="E30">
-        <v>1403.5</v>
+        <v>1406</v>
       </c>
       <c r="F30">
-        <v>1411</v>
+        <v>1413.5</v>
       </c>
       <c r="G30" t="str">
         <v>경유</v>
@@ -1288,10 +1288,10 @@
         <v>운전자B</v>
       </c>
       <c r="E31">
-        <v>1411</v>
+        <v>1413.5</v>
       </c>
       <c r="F31">
-        <v>1417.5</v>
+        <v>1421</v>
       </c>
       <c r="G31" t="str">
         <v>경유</v>
@@ -1317,16 +1317,16 @@
         <v>운전자C</v>
       </c>
       <c r="E32">
-        <v>1417.5</v>
+        <v>1421</v>
       </c>
       <c r="F32">
-        <v>1423</v>
+        <v>1426.5</v>
       </c>
       <c r="G32" t="str">
         <v>경유</v>
       </c>
       <c r="H32">
-        <v>49.3</v>
+        <v>44.7</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1349,10 +1349,10 @@
         <v>운전자A</v>
       </c>
       <c r="E33">
-        <v>1423</v>
+        <v>1426.5</v>
       </c>
       <c r="F33">
-        <v>1428.5</v>
+        <v>1433</v>
       </c>
       <c r="G33" t="str">
         <v>경유</v>
@@ -1378,10 +1378,10 @@
         <v>운전자D</v>
       </c>
       <c r="E34">
-        <v>1428.5</v>
+        <v>1433</v>
       </c>
       <c r="F34">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="G34" t="str">
         <v>경유</v>
@@ -1407,16 +1407,16 @@
         <v>운전자A</v>
       </c>
       <c r="E35">
-        <v>1436</v>
+        <v>1441</v>
       </c>
       <c r="F35">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="G35" t="str">
         <v>경유</v>
       </c>
       <c r="H35">
-        <v>50.2</v>
+        <v>46.5</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1439,10 +1439,10 @@
         <v>운전자B</v>
       </c>
       <c r="E36">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="F36">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="G36" t="str">
         <v>경유</v>
@@ -1468,10 +1468,10 @@
         <v>운전자D</v>
       </c>
       <c r="E37">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="F37">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="G37" t="str">
         <v>경유</v>
@@ -1497,19 +1497,19 @@
         <v>운전자C</v>
       </c>
       <c r="E38">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F38">
-        <v>1461</v>
+        <v>1468</v>
       </c>
       <c r="G38" t="str">
         <v>경유</v>
       </c>
       <c r="I38" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>IMG_20260805_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1526,16 +1526,16 @@
         <v>운전자D</v>
       </c>
       <c r="E39">
-        <v>1461</v>
+        <v>1468</v>
       </c>
       <c r="F39">
-        <v>1466</v>
+        <v>1475.5</v>
       </c>
       <c r="G39" t="str">
         <v>경유</v>
       </c>
       <c r="H39">
-        <v>40.9</v>
+        <v>59.5</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1558,10 +1558,10 @@
         <v>운전자B</v>
       </c>
       <c r="E40">
-        <v>1466</v>
+        <v>1475.5</v>
       </c>
       <c r="F40">
-        <v>1474</v>
+        <v>1480.5</v>
       </c>
       <c r="G40" t="str">
         <v>경유</v>
@@ -1587,10 +1587,10 @@
         <v>운전자A</v>
       </c>
       <c r="E41">
-        <v>1474</v>
+        <v>1480.5</v>
       </c>
       <c r="F41">
-        <v>1481</v>
+        <v>1486</v>
       </c>
       <c r="G41" t="str">
         <v>경유</v>
@@ -1616,16 +1616,16 @@
         <v>운전자B</v>
       </c>
       <c r="E42">
-        <v>1481</v>
+        <v>1486</v>
       </c>
       <c r="F42">
-        <v>1488.5</v>
+        <v>1494</v>
       </c>
       <c r="G42" t="str">
         <v>경유</v>
       </c>
       <c r="H42">
-        <v>59.5</v>
+        <v>62.1</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1648,10 +1648,10 @@
         <v>운전자C</v>
       </c>
       <c r="E43">
-        <v>1488.5</v>
+        <v>1494</v>
       </c>
       <c r="F43">
-        <v>1493.5</v>
+        <v>1500.5</v>
       </c>
       <c r="G43" t="str">
         <v>경유</v>
@@ -1677,10 +1677,10 @@
         <v>운전자A</v>
       </c>
       <c r="E44">
-        <v>1493.5</v>
+        <v>1500.5</v>
       </c>
       <c r="F44">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="G44" t="str">
         <v>경유</v>
@@ -1706,19 +1706,19 @@
         <v>운전자D</v>
       </c>
       <c r="E45">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="F45">
-        <v>1508.5</v>
+        <v>1513.5</v>
       </c>
       <c r="G45" t="str">
         <v>경유</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>IMG_20260812_1(예시).jpg</v>
       </c>
     </row>
     <row r="46">
@@ -1735,22 +1735,22 @@
         <v>운전자A</v>
       </c>
       <c r="E46">
-        <v>1508.5</v>
+        <v>1513.5</v>
       </c>
       <c r="F46">
-        <v>1514.5</v>
+        <v>1521.5</v>
       </c>
       <c r="G46" t="str">
         <v>경유</v>
       </c>
       <c r="H46">
-        <v>54.5</v>
+        <v>70</v>
       </c>
       <c r="I46" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J46" t="str">
-        <v>IMG_20260813_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1767,19 +1767,19 @@
         <v>운전자C</v>
       </c>
       <c r="E47">
-        <v>1514.5</v>
+        <v>1521.5</v>
       </c>
       <c r="F47">
-        <v>1521</v>
+        <v>1527.5</v>
       </c>
       <c r="G47" t="str">
         <v>경유</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>IMG_20260813_1(예시).jpg</v>
       </c>
     </row>
     <row r="48">
@@ -1796,10 +1796,10 @@
         <v>운전자B</v>
       </c>
       <c r="E48">
-        <v>1521</v>
+        <v>1527.5</v>
       </c>
       <c r="F48">
-        <v>1527.5</v>
+        <v>1534.5</v>
       </c>
       <c r="G48" t="str">
         <v>경유</v>
@@ -1825,16 +1825,16 @@
         <v>운전자C</v>
       </c>
       <c r="E49">
-        <v>1527.5</v>
+        <v>1534.5</v>
       </c>
       <c r="F49">
-        <v>1532.5</v>
+        <v>1541.5</v>
       </c>
       <c r="G49" t="str">
         <v>경유</v>
       </c>
       <c r="H49">
-        <v>43.9</v>
+        <v>59.4</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1857,10 +1857,10 @@
         <v>운전자D</v>
       </c>
       <c r="E50">
-        <v>1532.5</v>
+        <v>1541.5</v>
       </c>
       <c r="F50">
-        <v>1537.5</v>
+        <v>1549</v>
       </c>
       <c r="G50" t="str">
         <v>경유</v>
@@ -1886,19 +1886,19 @@
         <v>운전자B</v>
       </c>
       <c r="E51">
-        <v>1537.5</v>
+        <v>1549</v>
       </c>
       <c r="F51">
-        <v>1543.5</v>
+        <v>1554</v>
       </c>
       <c r="G51" t="str">
         <v>경유</v>
       </c>
       <c r="I51" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J51" t="str">
-        <v>IMG_20260818_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -1915,10 +1915,10 @@
         <v>운전자A</v>
       </c>
       <c r="E52">
-        <v>1543.5</v>
+        <v>1554</v>
       </c>
       <c r="F52">
-        <v>1550.5</v>
+        <v>1561</v>
       </c>
       <c r="G52" t="str">
         <v>경유</v>
@@ -1944,16 +1944,16 @@
         <v>운전자B</v>
       </c>
       <c r="E53">
-        <v>1550.5</v>
+        <v>1561</v>
       </c>
       <c r="F53">
-        <v>1557.5</v>
+        <v>1566</v>
       </c>
       <c r="G53" t="str">
         <v>경유</v>
       </c>
       <c r="H53">
-        <v>59.4</v>
+        <v>40.9</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1976,10 +1976,10 @@
         <v>운전자D</v>
       </c>
       <c r="E54">
-        <v>1557.5</v>
+        <v>1566</v>
       </c>
       <c r="F54">
-        <v>1564.5</v>
+        <v>1573</v>
       </c>
       <c r="G54" t="str">
         <v>경유</v>
@@ -2005,19 +2005,19 @@
         <v>운전자C</v>
       </c>
       <c r="E55">
-        <v>1564.5</v>
+        <v>1573</v>
       </c>
       <c r="F55">
-        <v>1571.5</v>
+        <v>1578.5</v>
       </c>
       <c r="G55" t="str">
         <v>경유</v>
       </c>
       <c r="I55" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
       <c r="J55" t="str">
-        <v>IMG_20260821_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2034,22 +2034,22 @@
         <v>운전자D</v>
       </c>
       <c r="E56">
-        <v>1571.5</v>
+        <v>1578.5</v>
       </c>
       <c r="F56">
-        <v>1578.5</v>
+        <v>1584.5</v>
       </c>
       <c r="G56" t="str">
         <v>경유</v>
       </c>
       <c r="H56">
-        <v>55</v>
+        <v>45.8</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>IMG_20260824_1(예시).jpg</v>
       </c>
     </row>
     <row r="57">
@@ -2066,10 +2066,10 @@
         <v>운전자A</v>
       </c>
       <c r="E57">
-        <v>1578.5</v>
+        <v>1584.5</v>
       </c>
       <c r="F57">
-        <v>1584.5</v>
+        <v>1591</v>
       </c>
       <c r="G57" t="str">
         <v>경유</v>
@@ -2095,19 +2095,19 @@
         <v>운전자C</v>
       </c>
       <c r="E58">
-        <v>1584.5</v>
+        <v>1591</v>
       </c>
       <c r="F58">
-        <v>1592.5</v>
+        <v>1598.5</v>
       </c>
       <c r="G58" t="str">
         <v>경유</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>IMG_20260825_1(예시).jpg</v>
       </c>
     </row>
     <row r="59">
@@ -2124,10 +2124,10 @@
         <v>운전자B</v>
       </c>
       <c r="E59">
-        <v>1592.5</v>
+        <v>1598.5</v>
       </c>
       <c r="F59">
-        <v>1599.5</v>
+        <v>1606</v>
       </c>
       <c r="G59" t="str">
         <v>경유</v>
@@ -2153,22 +2153,22 @@
         <v>운전자C</v>
       </c>
       <c r="E60">
-        <v>1599.5</v>
+        <v>1606</v>
       </c>
       <c r="F60">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="G60" t="str">
         <v>경유</v>
       </c>
       <c r="H60">
-        <v>53.6</v>
+        <v>64.8</v>
       </c>
       <c r="I60" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v/>
       </c>
       <c r="J60" t="str">
-        <v>IMG_20260827_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -2185,16 +2185,16 @@
         <v>운전자A</v>
       </c>
       <c r="E61">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="F61">
-        <v>1611</v>
+        <v>1619</v>
       </c>
       <c r="G61" t="str">
         <v>경유</v>
       </c>
       <c r="I61" t="str">
-        <v>운전석 계기판 화면 깜빡임(예시)</v>
+        <v>충전 커넥터 체결 불량(예시)</v>
       </c>
       <c r="J61" t="str">
         <v>IMG_20260827_1(예시).jpg</v>
@@ -2214,10 +2214,10 @@
         <v>운전자D</v>
       </c>
       <c r="E62">
-        <v>1611</v>
+        <v>1619</v>
       </c>
       <c r="F62">
-        <v>1619</v>
+        <v>1626</v>
       </c>
       <c r="G62" t="str">
         <v>경유</v>
@@ -2243,16 +2243,16 @@
         <v>운전자A</v>
       </c>
       <c r="E63">
-        <v>1619</v>
+        <v>1626</v>
       </c>
       <c r="F63">
-        <v>1624.5</v>
+        <v>1632</v>
       </c>
       <c r="G63" t="str">
         <v>경유</v>
       </c>
       <c r="H63">
-        <v>44.9</v>
+        <v>52.1</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2275,10 +2275,10 @@
         <v>운전자B</v>
       </c>
       <c r="E64">
-        <v>1624.5</v>
+        <v>1632</v>
       </c>
       <c r="F64">
-        <v>1632</v>
+        <v>1638</v>
       </c>
       <c r="G64" t="str">
         <v>경유</v>
@@ -2304,10 +2304,10 @@
         <v>운전자D</v>
       </c>
       <c r="E65">
-        <v>1632</v>
+        <v>1638</v>
       </c>
       <c r="F65">
-        <v>1638</v>
+        <v>1644.5</v>
       </c>
       <c r="G65" t="str">
         <v>경유</v>
@@ -2333,19 +2333,19 @@
         <v>운전자C</v>
       </c>
       <c r="E66">
-        <v>1638</v>
+        <v>1644.5</v>
       </c>
       <c r="F66">
-        <v>1643</v>
+        <v>1651.5</v>
       </c>
       <c r="G66" t="str">
         <v>경유</v>
       </c>
       <c r="I66" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
       <c r="J66" t="str">
-        <v>IMG_20260902_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -2362,16 +2362,16 @@
         <v>운전자D</v>
       </c>
       <c r="E67">
-        <v>1643</v>
+        <v>1651.5</v>
       </c>
       <c r="F67">
-        <v>1650</v>
+        <v>1656.5</v>
       </c>
       <c r="G67" t="str">
         <v>경유</v>
       </c>
       <c r="H67">
-        <v>57.2</v>
+        <v>38.3</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2394,10 +2394,10 @@
         <v>운전자B</v>
       </c>
       <c r="E68">
-        <v>1650</v>
+        <v>1656.5</v>
       </c>
       <c r="F68">
-        <v>1656</v>
+        <v>1662</v>
       </c>
       <c r="G68" t="str">
         <v>경유</v>
@@ -2423,10 +2423,10 @@
         <v>운전자A</v>
       </c>
       <c r="E69">
-        <v>1656</v>
+        <v>1662</v>
       </c>
       <c r="F69">
-        <v>1662.5</v>
+        <v>1667</v>
       </c>
       <c r="G69" t="str">
         <v>경유</v>
@@ -2452,16 +2452,16 @@
         <v>운전자B</v>
       </c>
       <c r="E70">
-        <v>1662.5</v>
+        <v>1667</v>
       </c>
       <c r="F70">
-        <v>1668.5</v>
+        <v>1673</v>
       </c>
       <c r="G70" t="str">
         <v>경유</v>
       </c>
       <c r="H70">
-        <v>50.6</v>
+        <v>53.2</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2484,10 +2484,10 @@
         <v>운전자C</v>
       </c>
       <c r="E71">
-        <v>1668.5</v>
+        <v>1673</v>
       </c>
       <c r="F71">
-        <v>1675.5</v>
+        <v>1678.5</v>
       </c>
       <c r="G71" t="str">
         <v>경유</v>
@@ -2513,19 +2513,19 @@
         <v>운전자A</v>
       </c>
       <c r="E72">
-        <v>1675.5</v>
+        <v>1678.5</v>
       </c>
       <c r="F72">
-        <v>1682.5</v>
+        <v>1684.5</v>
       </c>
       <c r="G72" t="str">
         <v>경유</v>
       </c>
       <c r="I72" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v/>
       </c>
       <c r="J72" t="str">
-        <v>IMG_20260908_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -2542,10 +2542,10 @@
         <v>운전자D</v>
       </c>
       <c r="E73">
-        <v>1682.5</v>
+        <v>1684.5</v>
       </c>
       <c r="F73">
-        <v>1689</v>
+        <v>1689.5</v>
       </c>
       <c r="G73" t="str">
         <v>경유</v>
@@ -2571,7 +2571,7 @@
         <v>운전자A</v>
       </c>
       <c r="E74">
-        <v>1689</v>
+        <v>1689.5</v>
       </c>
       <c r="F74">
         <v>1696.5</v>
@@ -2580,7 +2580,7 @@
         <v>경유</v>
       </c>
       <c r="H74">
-        <v>58</v>
+        <v>61.8</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2606,7 +2606,7 @@
         <v>1696.5</v>
       </c>
       <c r="F75">
-        <v>1701.5</v>
+        <v>1702.5</v>
       </c>
       <c r="G75" t="str">
         <v>경유</v>
@@ -2632,10 +2632,10 @@
         <v>운전자B</v>
       </c>
       <c r="E76">
-        <v>1701.5</v>
+        <v>1702.5</v>
       </c>
       <c r="F76">
-        <v>1708</v>
+        <v>1707.5</v>
       </c>
       <c r="G76" t="str">
         <v>경유</v>
@@ -2661,16 +2661,16 @@
         <v>운전자C</v>
       </c>
       <c r="E77">
-        <v>1708</v>
+        <v>1707.5</v>
       </c>
       <c r="F77">
-        <v>1713.5</v>
+        <v>1712.5</v>
       </c>
       <c r="G77" t="str">
         <v>경유</v>
       </c>
       <c r="H77">
-        <v>46.6</v>
+        <v>38</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2693,19 +2693,19 @@
         <v>운전자D</v>
       </c>
       <c r="E78">
-        <v>1713.5</v>
+        <v>1712.5</v>
       </c>
       <c r="F78">
-        <v>1720</v>
+        <v>1720.5</v>
       </c>
       <c r="G78" t="str">
         <v>경유</v>
       </c>
       <c r="I78" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J78" t="str">
-        <v>IMG_20260915_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -2722,10 +2722,10 @@
         <v>운전자B</v>
       </c>
       <c r="E79">
-        <v>1720</v>
+        <v>1720.5</v>
       </c>
       <c r="F79">
-        <v>1726</v>
+        <v>1727.5</v>
       </c>
       <c r="G79" t="str">
         <v>경유</v>
@@ -2751,10 +2751,10 @@
         <v>운전자A</v>
       </c>
       <c r="E80">
-        <v>1726</v>
+        <v>1727.5</v>
       </c>
       <c r="F80">
-        <v>1731.5</v>
+        <v>1735.5</v>
       </c>
       <c r="G80" t="str">
         <v>경유</v>
@@ -2780,22 +2780,22 @@
         <v>운전자B</v>
       </c>
       <c r="E81">
-        <v>1731.5</v>
+        <v>1735.5</v>
       </c>
       <c r="F81">
-        <v>1739</v>
+        <v>1741.5</v>
       </c>
       <c r="G81" t="str">
         <v>경유</v>
       </c>
       <c r="H81">
-        <v>58.4</v>
+        <v>46.9</v>
       </c>
       <c r="I81" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J81" t="str">
-        <v>IMG_20260917_1(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -2812,16 +2812,16 @@
         <v>운전자D</v>
       </c>
       <c r="E82">
-        <v>1739</v>
+        <v>1741.5</v>
       </c>
       <c r="F82">
-        <v>1744.5</v>
+        <v>1749.5</v>
       </c>
       <c r="G82" t="str">
         <v>경유</v>
       </c>
       <c r="I82" t="str">
-        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J82" t="str">
         <v>IMG_20260917_1(예시).jpg</v>
@@ -2841,10 +2841,10 @@
         <v>운전자C</v>
       </c>
       <c r="E83">
-        <v>1744.5</v>
+        <v>1749.5</v>
       </c>
       <c r="F83">
-        <v>1751.5</v>
+        <v>1755.5</v>
       </c>
       <c r="G83" t="str">
         <v>경유</v>
@@ -2870,22 +2870,22 @@
         <v>운전자D</v>
       </c>
       <c r="E84">
-        <v>1751.5</v>
+        <v>1755.5</v>
       </c>
       <c r="F84">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="G84" t="str">
         <v>경유</v>
       </c>
       <c r="H84">
-        <v>47</v>
+        <v>43.7</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J84" t="str">
-        <v/>
+        <v>IMG_20260921_1(예시).jpg</v>
       </c>
     </row>
     <row r="85">
@@ -2902,10 +2902,10 @@
         <v>운전자A</v>
       </c>
       <c r="E85">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="F85">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G85" t="str">
         <v>경유</v>
@@ -2931,10 +2931,10 @@
         <v>운전자C</v>
       </c>
       <c r="E86">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="F86">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G86" t="str">
         <v>경유</v>
@@ -2960,10 +2960,10 @@
         <v>운전자B</v>
       </c>
       <c r="E87">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="F87">
-        <v>1777.5</v>
+        <v>1780</v>
       </c>
       <c r="G87" t="str">
         <v>경유</v>
@@ -2989,16 +2989,16 @@
         <v>운전자C</v>
       </c>
       <c r="E88">
-        <v>1777.5</v>
+        <v>1780</v>
       </c>
       <c r="F88">
-        <v>1782.5</v>
+        <v>1787.5</v>
       </c>
       <c r="G88" t="str">
         <v>경유</v>
       </c>
       <c r="H88">
-        <v>42.8</v>
+        <v>60.8</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3021,10 +3021,10 @@
         <v>운전자A</v>
       </c>
       <c r="E89">
-        <v>1782.5</v>
+        <v>1787.5</v>
       </c>
       <c r="F89">
-        <v>1788.5</v>
+        <v>1793.5</v>
       </c>
       <c r="G89" t="str">
         <v>경유</v>
@@ -3050,10 +3050,10 @@
         <v>운전자D</v>
       </c>
       <c r="E90">
-        <v>1788.5</v>
+        <v>1793.5</v>
       </c>
       <c r="F90">
-        <v>1794</v>
+        <v>1800</v>
       </c>
       <c r="G90" t="str">
         <v>경유</v>
@@ -3159,19 +3159,19 @@
         <v>861.5</v>
       </c>
       <c r="F4">
-        <v>866.5</v>
+        <v>867</v>
       </c>
       <c r="G4" t="str">
         <v>LPG</v>
       </c>
       <c r="H4">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>IMG_20260702_2(예시).jpg</v>
       </c>
     </row>
     <row r="5">
@@ -3188,10 +3188,10 @@
         <v>운전자A</v>
       </c>
       <c r="E5">
-        <v>866.5</v>
+        <v>867</v>
       </c>
       <c r="F5">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G5" t="str">
         <v>LPG</v>
@@ -3217,16 +3217,16 @@
         <v>운전자B</v>
       </c>
       <c r="E6">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F6">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G6" t="str">
         <v>LPG</v>
       </c>
       <c r="H6">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -3249,10 +3249,10 @@
         <v>운전자C</v>
       </c>
       <c r="E7">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F7">
-        <v>883.5</v>
+        <v>883</v>
       </c>
       <c r="G7" t="str">
         <v>LPG</v>
@@ -3278,10 +3278,10 @@
         <v>운전자D</v>
       </c>
       <c r="E8">
-        <v>883.5</v>
+        <v>883</v>
       </c>
       <c r="F8">
-        <v>890</v>
+        <v>890.5</v>
       </c>
       <c r="G8" t="str">
         <v>LPG</v>
@@ -3307,7 +3307,7 @@
         <v>운전자A</v>
       </c>
       <c r="E9">
-        <v>890</v>
+        <v>890.5</v>
       </c>
       <c r="F9">
         <v>897</v>
@@ -3316,7 +3316,7 @@
         <v>LPG</v>
       </c>
       <c r="H9">
-        <v>58.7</v>
+        <v>54.4</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -3342,7 +3342,7 @@
         <v>897</v>
       </c>
       <c r="F10">
-        <v>902.5</v>
+        <v>903.5</v>
       </c>
       <c r="G10" t="str">
         <v>LPG</v>
@@ -3368,10 +3368,10 @@
         <v>운전자D</v>
       </c>
       <c r="E11">
-        <v>902.5</v>
+        <v>903.5</v>
       </c>
       <c r="F11">
-        <v>909</v>
+        <v>908.5</v>
       </c>
       <c r="G11" t="str">
         <v>LPG</v>
@@ -3397,7 +3397,7 @@
         <v>운전자A</v>
       </c>
       <c r="E12">
-        <v>909</v>
+        <v>908.5</v>
       </c>
       <c r="F12">
         <v>916</v>
@@ -3429,13 +3429,13 @@
         <v>916</v>
       </c>
       <c r="F13">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G13" t="str">
         <v>LPG</v>
       </c>
       <c r="H13">
-        <v>73.1</v>
+        <v>61.3</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -3458,10 +3458,10 @@
         <v>운전자C</v>
       </c>
       <c r="E14">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="F14">
-        <v>931</v>
+        <v>928.5</v>
       </c>
       <c r="G14" t="str">
         <v>LPG</v>
@@ -3487,22 +3487,22 @@
         <v>운전자D</v>
       </c>
       <c r="E15">
-        <v>931</v>
+        <v>928.5</v>
       </c>
       <c r="F15">
-        <v>937</v>
+        <v>935.5</v>
       </c>
       <c r="G15" t="str">
         <v>LPG</v>
       </c>
       <c r="H15">
-        <v>55.1</v>
+        <v>60.4</v>
       </c>
       <c r="I15" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J15" t="str">
-        <v>IMG_20260720_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3519,10 +3519,10 @@
         <v>운전자A</v>
       </c>
       <c r="E16">
-        <v>937</v>
+        <v>935.5</v>
       </c>
       <c r="F16">
-        <v>943.5</v>
+        <v>943</v>
       </c>
       <c r="G16" t="str">
         <v>LPG</v>
@@ -3548,19 +3548,19 @@
         <v>운전자B</v>
       </c>
       <c r="E17">
-        <v>943.5</v>
+        <v>943</v>
       </c>
       <c r="F17">
-        <v>948.5</v>
+        <v>949.5</v>
       </c>
       <c r="G17" t="str">
         <v>LPG</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>IMG_20260722_2(예시).jpg</v>
       </c>
     </row>
     <row r="18">
@@ -3577,16 +3577,16 @@
         <v>운전자C</v>
       </c>
       <c r="E18">
-        <v>948.5</v>
+        <v>949.5</v>
       </c>
       <c r="F18">
-        <v>956</v>
+        <v>957.5</v>
       </c>
       <c r="G18" t="str">
         <v>LPG</v>
       </c>
       <c r="H18">
-        <v>70.9</v>
+        <v>80.2</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -3609,10 +3609,10 @@
         <v>운전자D</v>
       </c>
       <c r="E19">
-        <v>956</v>
+        <v>957.5</v>
       </c>
       <c r="F19">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G19" t="str">
         <v>LPG</v>
@@ -3638,16 +3638,16 @@
         <v>운전자A</v>
       </c>
       <c r="E20">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F20">
-        <v>970.5</v>
+        <v>968</v>
       </c>
       <c r="G20" t="str">
         <v>LPG</v>
       </c>
       <c r="H20">
-        <v>55.3</v>
+        <v>45.3</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -3670,19 +3670,19 @@
         <v>운전자B</v>
       </c>
       <c r="E21">
-        <v>970.5</v>
+        <v>968</v>
       </c>
       <c r="F21">
-        <v>977.5</v>
+        <v>973.5</v>
       </c>
       <c r="G21" t="str">
         <v>LPG</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>IMG_20260728_2(예시).jpg</v>
       </c>
     </row>
     <row r="22">
@@ -3699,10 +3699,10 @@
         <v>운전자C</v>
       </c>
       <c r="E22">
-        <v>977.5</v>
+        <v>973.5</v>
       </c>
       <c r="F22">
-        <v>984.5</v>
+        <v>978.5</v>
       </c>
       <c r="G22" t="str">
         <v>LPG</v>
@@ -3728,22 +3728,22 @@
         <v>운전자D</v>
       </c>
       <c r="E23">
-        <v>984.5</v>
+        <v>978.5</v>
       </c>
       <c r="F23">
-        <v>991</v>
+        <v>983.5</v>
       </c>
       <c r="G23" t="str">
         <v>LPG</v>
       </c>
       <c r="H23">
-        <v>60.5</v>
+        <v>50.9</v>
       </c>
       <c r="I23" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v/>
       </c>
       <c r="J23" t="str">
-        <v>IMG_20260730_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -3760,16 +3760,16 @@
         <v>운전자B</v>
       </c>
       <c r="E24">
+        <v>983.5</v>
+      </c>
+      <c r="F24">
         <v>991</v>
-      </c>
-      <c r="F24">
-        <v>999</v>
       </c>
       <c r="G24" t="str">
         <v>LPG</v>
       </c>
       <c r="H24">
-        <v>80.2</v>
+        <v>68.4</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -3792,10 +3792,10 @@
         <v>운전자C</v>
       </c>
       <c r="E25">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="F25">
-        <v>1004.5</v>
+        <v>996</v>
       </c>
       <c r="G25" t="str">
         <v>LPG</v>
@@ -3821,10 +3821,10 @@
         <v>운전자D</v>
       </c>
       <c r="E26">
-        <v>1004.5</v>
+        <v>996</v>
       </c>
       <c r="F26">
-        <v>1009.5</v>
+        <v>1004</v>
       </c>
       <c r="G26" t="str">
         <v>LPG</v>
@@ -3850,22 +3850,22 @@
         <v>운전자A</v>
       </c>
       <c r="E27">
+        <v>1004</v>
+      </c>
+      <c r="F27">
         <v>1009.5</v>
-      </c>
-      <c r="F27">
-        <v>1015.5</v>
       </c>
       <c r="G27" t="str">
         <v>LPG</v>
       </c>
       <c r="H27">
-        <v>51.8</v>
+        <v>48.7</v>
       </c>
       <c r="I27" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J27" t="str">
-        <v>IMG_20260806_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -3882,10 +3882,10 @@
         <v>운전자B</v>
       </c>
       <c r="E28">
-        <v>1015.5</v>
+        <v>1009.5</v>
       </c>
       <c r="F28">
-        <v>1020.5</v>
+        <v>1014.5</v>
       </c>
       <c r="G28" t="str">
         <v>LPG</v>
@@ -3911,22 +3911,22 @@
         <v>운전자C</v>
       </c>
       <c r="E29">
-        <v>1020.5</v>
+        <v>1014.5</v>
       </c>
       <c r="F29">
-        <v>1025.5</v>
+        <v>1021.5</v>
       </c>
       <c r="G29" t="str">
         <v>LPG</v>
       </c>
       <c r="H29">
-        <v>50.9</v>
+        <v>69.3</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>IMG_20260810_2(예시).jpg</v>
       </c>
     </row>
     <row r="30">
@@ -3943,10 +3943,10 @@
         <v>운전자D</v>
       </c>
       <c r="E30">
-        <v>1025.5</v>
+        <v>1021.5</v>
       </c>
       <c r="F30">
-        <v>1033</v>
+        <v>1026.5</v>
       </c>
       <c r="G30" t="str">
         <v>LPG</v>
@@ -3972,19 +3972,19 @@
         <v>운전자A</v>
       </c>
       <c r="E31">
-        <v>1033</v>
+        <v>1026.5</v>
       </c>
       <c r="F31">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="G31" t="str">
         <v>LPG</v>
       </c>
       <c r="I31" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
       <c r="J31" t="str">
-        <v>IMG_20260812_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -4001,16 +4001,16 @@
         <v>운전자B</v>
       </c>
       <c r="E32">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="F32">
-        <v>1047</v>
+        <v>1038.5</v>
       </c>
       <c r="G32" t="str">
         <v>LPG</v>
       </c>
       <c r="H32">
-        <v>74.6</v>
+        <v>57</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -4033,10 +4033,10 @@
         <v>운전자C</v>
       </c>
       <c r="E33">
-        <v>1047</v>
+        <v>1038.5</v>
       </c>
       <c r="F33">
-        <v>1052.5</v>
+        <v>1045.5</v>
       </c>
       <c r="G33" t="str">
         <v>LPG</v>
@@ -4062,22 +4062,22 @@
         <v>운전자D</v>
       </c>
       <c r="E34">
-        <v>1052.5</v>
+        <v>1045.5</v>
       </c>
       <c r="F34">
-        <v>1057.5</v>
+        <v>1051</v>
       </c>
       <c r="G34" t="str">
         <v>LPG</v>
       </c>
       <c r="H34">
-        <v>47.4</v>
+        <v>50.6</v>
       </c>
       <c r="I34" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J34" t="str">
-        <v>IMG_20260817_2(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -4094,10 +4094,10 @@
         <v>운전자A</v>
       </c>
       <c r="E35">
-        <v>1057.5</v>
+        <v>1051</v>
       </c>
       <c r="F35">
-        <v>1062.5</v>
+        <v>1058</v>
       </c>
       <c r="G35" t="str">
         <v>LPG</v>
@@ -4123,10 +4123,10 @@
         <v>운전자B</v>
       </c>
       <c r="E36">
-        <v>1062.5</v>
+        <v>1058</v>
       </c>
       <c r="F36">
-        <v>1067.5</v>
+        <v>1066</v>
       </c>
       <c r="G36" t="str">
         <v>LPG</v>
@@ -4152,16 +4152,16 @@
         <v>운전자C</v>
       </c>
       <c r="E37">
-        <v>1067.5</v>
+        <v>1066</v>
       </c>
       <c r="F37">
-        <v>1073</v>
+        <v>1072.5</v>
       </c>
       <c r="G37" t="str">
         <v>LPG</v>
       </c>
       <c r="H37">
-        <v>54</v>
+        <v>66.4</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -4184,10 +4184,10 @@
         <v>운전자D</v>
       </c>
       <c r="E38">
-        <v>1073</v>
+        <v>1072.5</v>
       </c>
       <c r="F38">
-        <v>1078.5</v>
+        <v>1079.5</v>
       </c>
       <c r="G38" t="str">
         <v>LPG</v>
@@ -4213,16 +4213,16 @@
         <v>운전자A</v>
       </c>
       <c r="E39">
-        <v>1078.5</v>
+        <v>1079.5</v>
       </c>
       <c r="F39">
-        <v>1085.5</v>
+        <v>1087</v>
       </c>
       <c r="G39" t="str">
         <v>LPG</v>
       </c>
       <c r="H39">
-        <v>64.2</v>
+        <v>63.7</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>운전자B</v>
       </c>
       <c r="E40">
-        <v>1085.5</v>
+        <v>1087</v>
       </c>
       <c r="F40">
         <v>1092</v>
@@ -4277,7 +4277,7 @@
         <v>1092</v>
       </c>
       <c r="F41">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G41" t="str">
         <v>LPG</v>
@@ -4303,16 +4303,16 @@
         <v>운전자D</v>
       </c>
       <c r="E42">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F42">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G42" t="str">
         <v>LPG</v>
       </c>
       <c r="H42">
-        <v>77</v>
+        <v>74.7</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -4335,10 +4335,10 @@
         <v>운전자A</v>
       </c>
       <c r="E43">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F43">
-        <v>1115</v>
+        <v>1113.5</v>
       </c>
       <c r="G43" t="str">
         <v>LPG</v>
@@ -4364,16 +4364,16 @@
         <v>운전자B</v>
       </c>
       <c r="E44">
-        <v>1115</v>
+        <v>1113.5</v>
       </c>
       <c r="F44">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G44" t="str">
         <v>LPG</v>
       </c>
       <c r="H44">
-        <v>67.3</v>
+        <v>76.1</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -4396,10 +4396,10 @@
         <v>운전자C</v>
       </c>
       <c r="E45">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F45">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="G45" t="str">
         <v>LPG</v>
@@ -4425,10 +4425,10 @@
         <v>운전자D</v>
       </c>
       <c r="E46">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="F46">
-        <v>1132</v>
+        <v>1136.5</v>
       </c>
       <c r="G46" t="str">
         <v>LPG</v>
@@ -4454,16 +4454,16 @@
         <v>운전자A</v>
       </c>
       <c r="E47">
-        <v>1132</v>
+        <v>1136.5</v>
       </c>
       <c r="F47">
-        <v>1138</v>
+        <v>1141.5</v>
       </c>
       <c r="G47" t="str">
         <v>LPG</v>
       </c>
       <c r="H47">
-        <v>57</v>
+        <v>50.4</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -4486,10 +4486,10 @@
         <v>운전자B</v>
       </c>
       <c r="E48">
-        <v>1138</v>
+        <v>1141.5</v>
       </c>
       <c r="F48">
-        <v>1144.5</v>
+        <v>1149</v>
       </c>
       <c r="G48" t="str">
         <v>LPG</v>
@@ -4515,16 +4515,16 @@
         <v>운전자C</v>
       </c>
       <c r="E49">
-        <v>1144.5</v>
+        <v>1149</v>
       </c>
       <c r="F49">
-        <v>1152</v>
+        <v>1155.5</v>
       </c>
       <c r="G49" t="str">
         <v>LPG</v>
       </c>
       <c r="H49">
-        <v>68.1</v>
+        <v>57.6</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -4547,10 +4547,10 @@
         <v>운전자D</v>
       </c>
       <c r="E50">
-        <v>1152</v>
+        <v>1155.5</v>
       </c>
       <c r="F50">
-        <v>1160</v>
+        <v>1161.5</v>
       </c>
       <c r="G50" t="str">
         <v>LPG</v>
@@ -4576,7 +4576,7 @@
         <v>운전자A</v>
       </c>
       <c r="E51">
-        <v>1160</v>
+        <v>1161.5</v>
       </c>
       <c r="F51">
         <v>1168</v>
@@ -4585,10 +4585,10 @@
         <v>LPG</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>IMG_20260909_2(예시).jpg</v>
       </c>
     </row>
     <row r="52">
@@ -4608,13 +4608,13 @@
         <v>1168</v>
       </c>
       <c r="F52">
-        <v>1175.5</v>
+        <v>1174.5</v>
       </c>
       <c r="G52" t="str">
         <v>LPG</v>
       </c>
       <c r="H52">
-        <v>67</v>
+        <v>65.6</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -4637,10 +4637,10 @@
         <v>운전자C</v>
       </c>
       <c r="E53">
-        <v>1175.5</v>
+        <v>1174.5</v>
       </c>
       <c r="F53">
-        <v>1183.5</v>
+        <v>1182</v>
       </c>
       <c r="G53" t="str">
         <v>LPG</v>
@@ -4666,16 +4666,16 @@
         <v>운전자D</v>
       </c>
       <c r="E54">
-        <v>1183.5</v>
+        <v>1182</v>
       </c>
       <c r="F54">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G54" t="str">
         <v>LPG</v>
       </c>
       <c r="H54">
-        <v>65.6</v>
+        <v>61.4</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -4698,10 +4698,10 @@
         <v>운전자A</v>
       </c>
       <c r="E55">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F55">
-        <v>1196.5</v>
+        <v>1195.5</v>
       </c>
       <c r="G55" t="str">
         <v>LPG</v>
@@ -4727,19 +4727,19 @@
         <v>운전자B</v>
       </c>
       <c r="E56">
-        <v>1196.5</v>
+        <v>1195.5</v>
       </c>
       <c r="F56">
-        <v>1202.5</v>
+        <v>1200.5</v>
       </c>
       <c r="G56" t="str">
         <v>LPG</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>IMG_20260916_2(예시).jpg</v>
       </c>
     </row>
     <row r="57">
@@ -4756,16 +4756,16 @@
         <v>운전자C</v>
       </c>
       <c r="E57">
-        <v>1202.5</v>
+        <v>1200.5</v>
       </c>
       <c r="F57">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="G57" t="str">
         <v>LPG</v>
       </c>
       <c r="H57">
-        <v>55.5</v>
+        <v>47.5</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -4788,19 +4788,19 @@
         <v>운전자D</v>
       </c>
       <c r="E58">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="F58">
-        <v>1215.5</v>
+        <v>1214</v>
       </c>
       <c r="G58" t="str">
         <v>LPG</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>포크 하강 속도 느려짐(예시)</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>IMG_20260918_2(예시).jpg</v>
       </c>
     </row>
     <row r="59">
@@ -4817,16 +4817,16 @@
         <v>운전자A</v>
       </c>
       <c r="E59">
-        <v>1215.5</v>
+        <v>1214</v>
       </c>
       <c r="F59">
-        <v>1221.5</v>
+        <v>1220</v>
       </c>
       <c r="G59" t="str">
         <v>LPG</v>
       </c>
       <c r="H59">
-        <v>58.5</v>
+        <v>55.9</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -4849,10 +4849,10 @@
         <v>운전자B</v>
       </c>
       <c r="E60">
-        <v>1221.5</v>
+        <v>1220</v>
       </c>
       <c r="F60">
-        <v>1228.5</v>
+        <v>1225.5</v>
       </c>
       <c r="G60" t="str">
         <v>LPG</v>
@@ -4878,10 +4878,10 @@
         <v>운전자C</v>
       </c>
       <c r="E61">
-        <v>1228.5</v>
+        <v>1225.5</v>
       </c>
       <c r="F61">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="G61" t="str">
         <v>LPG</v>
@@ -4907,19 +4907,19 @@
         <v>운전자D</v>
       </c>
       <c r="E62">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="F62">
-        <v>1241</v>
+        <v>1237.5</v>
       </c>
       <c r="G62" t="str">
         <v>LPG</v>
       </c>
       <c r="H62">
-        <v>42.8</v>
+        <v>51.1</v>
       </c>
       <c r="I62" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v>좌측 마스트 체인에서 소음 발생(예시)</v>
       </c>
       <c r="J62" t="str">
         <v>IMG_20260924_2(예시).jpg</v>
@@ -4939,10 +4939,10 @@
         <v>운전자A</v>
       </c>
       <c r="E63">
-        <v>1241</v>
+        <v>1237.5</v>
       </c>
       <c r="F63">
-        <v>1246.5</v>
+        <v>1243</v>
       </c>
       <c r="G63" t="str">
         <v>LPG</v>
@@ -5019,16 +5019,16 @@
         <v>432</v>
       </c>
       <c r="F3">
-        <v>440</v>
+        <v>439.5</v>
       </c>
       <c r="G3">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H3">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="I3" t="str">
-        <v>포크 하강 속도 느려짐(예시)</v>
+        <v>운전석 계기판 화면 깜빡임(예시)</v>
       </c>
       <c r="J3" t="str">
         <v>IMG_20260701_3(예시).jpg</v>
@@ -5048,16 +5048,16 @@
         <v>운전자A</v>
       </c>
       <c r="E4">
-        <v>440</v>
+        <v>439.5</v>
       </c>
       <c r="F4">
-        <v>446</v>
+        <v>444.5</v>
       </c>
       <c r="G4">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H4">
-        <v>23.4</v>
+        <v>28.5</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -5080,16 +5080,16 @@
         <v>운전자B</v>
       </c>
       <c r="E5">
-        <v>446</v>
+        <v>444.5</v>
       </c>
       <c r="F5">
-        <v>451.5</v>
+        <v>452.5</v>
       </c>
       <c r="G5">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H5">
-        <v>21.8</v>
+        <v>25</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -5112,16 +5112,16 @@
         <v>운전자C</v>
       </c>
       <c r="E6">
-        <v>451.5</v>
+        <v>452.5</v>
       </c>
       <c r="F6">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G6">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H6">
-        <v>22.1</v>
+        <v>26.6</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -5144,16 +5144,16 @@
         <v>운전자D</v>
       </c>
       <c r="E7">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F7">
-        <v>463</v>
+        <v>465.5</v>
       </c>
       <c r="G7">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H7">
-        <v>18.9</v>
+        <v>22.7</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -5176,16 +5176,16 @@
         <v>운전자A</v>
       </c>
       <c r="E8">
-        <v>463</v>
+        <v>465.5</v>
       </c>
       <c r="F8">
-        <v>469</v>
+        <v>471.5</v>
       </c>
       <c r="G8">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="H8">
-        <v>20.2</v>
+        <v>24.6</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -5208,16 +5208,16 @@
         <v>운전자B</v>
       </c>
       <c r="E9">
-        <v>469</v>
+        <v>471.5</v>
       </c>
       <c r="F9">
-        <v>474</v>
+        <v>479.5</v>
       </c>
       <c r="G9">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H9">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -5240,16 +5240,16 @@
         <v>운전자C</v>
       </c>
       <c r="E10">
-        <v>474</v>
+        <v>479.5</v>
       </c>
       <c r="F10">
-        <v>482</v>
+        <v>484.5</v>
       </c>
       <c r="G10">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H10">
-        <v>23.7</v>
+        <v>27.2</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -5272,16 +5272,16 @@
         <v>운전자D</v>
       </c>
       <c r="E11">
-        <v>482</v>
+        <v>484.5</v>
       </c>
       <c r="F11">
-        <v>489</v>
+        <v>489.5</v>
       </c>
       <c r="G11">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H11">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -5304,16 +5304,16 @@
         <v>운전자A</v>
       </c>
       <c r="E12">
-        <v>489</v>
+        <v>489.5</v>
       </c>
       <c r="F12">
-        <v>496.5</v>
+        <v>496</v>
       </c>
       <c r="G12">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H12">
-        <v>23.4</v>
+        <v>26.2</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -5336,16 +5336,16 @@
         <v/>
       </c>
       <c r="E13">
-        <v>496.5</v>
+        <v>496</v>
       </c>
       <c r="F13">
-        <v>503</v>
+        <v>502.5</v>
       </c>
       <c r="G13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H13">
-        <v>25.6</v>
+        <v>28.8</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -5368,16 +5368,16 @@
         <v>운전자C</v>
       </c>
       <c r="E14">
-        <v>503</v>
+        <v>502.5</v>
       </c>
       <c r="F14">
-        <v>510</v>
+        <v>508.5</v>
       </c>
       <c r="G14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H14">
-        <v>19.2</v>
+        <v>25.6</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -5400,16 +5400,16 @@
         <v>운전자D</v>
       </c>
       <c r="E15">
-        <v>510</v>
+        <v>508.5</v>
       </c>
       <c r="F15">
-        <v>516.5</v>
+        <v>513.5</v>
       </c>
       <c r="G15">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H15">
-        <v>24.6</v>
+        <v>22.7</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -5432,16 +5432,16 @@
         <v>운전자A</v>
       </c>
       <c r="E16">
-        <v>516.5</v>
+        <v>513.5</v>
       </c>
       <c r="F16">
-        <v>524.5</v>
+        <v>519.5</v>
       </c>
       <c r="G16">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H16">
-        <v>21.4</v>
+        <v>23</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -5464,16 +5464,16 @@
         <v>운전자B</v>
       </c>
       <c r="E17">
-        <v>524.5</v>
+        <v>519.5</v>
       </c>
       <c r="F17">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G17">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H17">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -5496,22 +5496,22 @@
         <v>운전자C</v>
       </c>
       <c r="E18">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="F18">
-        <v>539.5</v>
+        <v>532.5</v>
       </c>
       <c r="G18">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H18">
-        <v>26.6</v>
+        <v>25.9</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>IMG_20260722_3(예시).jpg</v>
       </c>
     </row>
     <row r="19">
@@ -5528,10 +5528,10 @@
         <v>운전자D</v>
       </c>
       <c r="E19">
-        <v>539.5</v>
+        <v>532.5</v>
       </c>
       <c r="F19">
-        <v>547.5</v>
+        <v>538.5</v>
       </c>
       <c r="G19">
         <v>82</v>
@@ -5560,16 +5560,16 @@
         <v>운전자A</v>
       </c>
       <c r="E20">
-        <v>547.5</v>
+        <v>538.5</v>
       </c>
       <c r="F20">
-        <v>554.5</v>
+        <v>545</v>
       </c>
       <c r="G20">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H20">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -5592,22 +5592,22 @@
         <v>운전자B</v>
       </c>
       <c r="E21">
-        <v>554.5</v>
+        <v>545</v>
       </c>
       <c r="F21">
-        <v>561</v>
+        <v>552.5</v>
       </c>
       <c r="G21">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H21">
-        <v>28.8</v>
+        <v>26.9</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>IMG_20260727_3(예시).jpg</v>
       </c>
     </row>
     <row r="22">
@@ -5624,16 +5624,16 @@
         <v>운전자C</v>
       </c>
       <c r="E22">
-        <v>561</v>
+        <v>552.5</v>
       </c>
       <c r="F22">
-        <v>567.5</v>
+        <v>560.5</v>
       </c>
       <c r="G22">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="H22">
-        <v>28.5</v>
+        <v>19.8</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -5656,16 +5656,16 @@
         <v>운전자D</v>
       </c>
       <c r="E23">
-        <v>567.5</v>
+        <v>560.5</v>
       </c>
       <c r="F23">
-        <v>573.5</v>
+        <v>566</v>
       </c>
       <c r="G23">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H23">
-        <v>23.7</v>
+        <v>17.9</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -5688,16 +5688,16 @@
         <v>운전자A</v>
       </c>
       <c r="E24">
-        <v>573.5</v>
+        <v>566</v>
       </c>
       <c r="F24">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="G24">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H24">
-        <v>18.6</v>
+        <v>21.1</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -5720,16 +5720,16 @@
         <v>운전자B</v>
       </c>
       <c r="E25">
+        <v>573</v>
+      </c>
+      <c r="F25">
         <v>581</v>
       </c>
-      <c r="F25">
-        <v>587</v>
-      </c>
       <c r="G25">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H25">
-        <v>26.2</v>
+        <v>24.6</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -5752,16 +5752,16 @@
         <v>운전자C</v>
       </c>
       <c r="E26">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F26">
-        <v>593.5</v>
+        <v>588</v>
       </c>
       <c r="G26">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H26">
-        <v>25.6</v>
+        <v>18.9</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -5784,22 +5784,22 @@
         <v>운전자D</v>
       </c>
       <c r="E27">
+        <v>588</v>
+      </c>
+      <c r="F27">
         <v>593.5</v>
       </c>
-      <c r="F27">
-        <v>601</v>
-      </c>
       <c r="G27">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H27">
-        <v>26.9</v>
+        <v>19.2</v>
       </c>
       <c r="I27" t="str">
-        <v>작동유 온도 경고등 점등 후 소등(예시)</v>
+        <v/>
       </c>
       <c r="J27" t="str">
-        <v>IMG_20260804_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -5816,16 +5816,16 @@
         <v>운전자A</v>
       </c>
       <c r="E28">
-        <v>601</v>
+        <v>593.5</v>
       </c>
       <c r="F28">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="G28">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="H28">
-        <v>19.8</v>
+        <v>27.2</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -5848,16 +5848,16 @@
         <v>운전자B</v>
       </c>
       <c r="E29">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="F29">
-        <v>614.5</v>
+        <v>605</v>
       </c>
       <c r="G29">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H29">
-        <v>17.9</v>
+        <v>19.8</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -5880,16 +5880,16 @@
         <v>운전자C</v>
       </c>
       <c r="E30">
-        <v>614.5</v>
+        <v>605</v>
       </c>
       <c r="F30">
-        <v>621.5</v>
+        <v>610.5</v>
       </c>
       <c r="G30">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H30">
-        <v>21.1</v>
+        <v>19.5</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -5912,16 +5912,16 @@
         <v>운전자D</v>
       </c>
       <c r="E31">
-        <v>621.5</v>
+        <v>610.5</v>
       </c>
       <c r="F31">
-        <v>629.5</v>
+        <v>616.5</v>
       </c>
       <c r="G31">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H31">
-        <v>24.6</v>
+        <v>23.4</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -5944,22 +5944,22 @@
         <v>운전자A</v>
       </c>
       <c r="E32">
-        <v>629.5</v>
+        <v>616.5</v>
       </c>
       <c r="F32">
-        <v>636.5</v>
+        <v>623</v>
       </c>
       <c r="G32">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H32">
-        <v>18.9</v>
+        <v>25.9</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>충전 커넥터 체결 불량(예시)</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>IMG_20260811_3(예시).jpg</v>
       </c>
     </row>
     <row r="33">
@@ -5976,16 +5976,16 @@
         <v>운전자B</v>
       </c>
       <c r="E33">
-        <v>636.5</v>
+        <v>623</v>
       </c>
       <c r="F33">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="G33">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="H33">
-        <v>19.2</v>
+        <v>25.9</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -6008,16 +6008,16 @@
         <v>운전자C</v>
       </c>
       <c r="E34">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="F34">
-        <v>648.5</v>
+        <v>637</v>
       </c>
       <c r="G34">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H34">
-        <v>27.2</v>
+        <v>21.8</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -6040,16 +6040,16 @@
         <v>운전자D</v>
       </c>
       <c r="E35">
-        <v>648.5</v>
+        <v>637</v>
       </c>
       <c r="F35">
-        <v>653.5</v>
+        <v>644.5</v>
       </c>
       <c r="G35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H35">
-        <v>19.8</v>
+        <v>21.1</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -6072,16 +6072,16 @@
         <v>운전자A</v>
       </c>
       <c r="E36">
-        <v>653.5</v>
+        <v>644.5</v>
       </c>
       <c r="F36">
-        <v>659</v>
+        <v>649.5</v>
       </c>
       <c r="G36">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H36">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -6104,22 +6104,22 @@
         <v>운전자B</v>
       </c>
       <c r="E37">
-        <v>659</v>
+        <v>649.5</v>
       </c>
       <c r="F37">
-        <v>665</v>
+        <v>657.5</v>
       </c>
       <c r="G37">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H37">
-        <v>23.4</v>
+        <v>28.5</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>운전석 계기판 화면 깜빡임(예시)</v>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>IMG_20260818_3(예시).jpg</v>
       </c>
     </row>
     <row r="38">
@@ -6136,22 +6136,22 @@
         <v>운전자C</v>
       </c>
       <c r="E38">
-        <v>665</v>
+        <v>657.5</v>
       </c>
       <c r="F38">
-        <v>671.5</v>
+        <v>663</v>
       </c>
       <c r="G38">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H38">
-        <v>25.9</v>
+        <v>22.1</v>
       </c>
       <c r="I38" t="str">
-        <v>충전 커넥터 체결 불량(예시)</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>IMG_20260819_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -6168,22 +6168,22 @@
         <v>운전자D</v>
       </c>
       <c r="E39">
-        <v>671.5</v>
+        <v>663</v>
       </c>
       <c r="F39">
-        <v>677.5</v>
+        <v>668.5</v>
       </c>
       <c r="G39">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="H39">
-        <v>25.9</v>
+        <v>21.1</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>IMG_20260820_3(예시).jpg</v>
       </c>
     </row>
     <row r="40">
@@ -6200,16 +6200,16 @@
         <v>운전자A</v>
       </c>
       <c r="E40">
-        <v>677.5</v>
+        <v>668.5</v>
       </c>
       <c r="F40">
-        <v>685.5</v>
+        <v>676.5</v>
       </c>
       <c r="G40">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H40">
-        <v>21.8</v>
+        <v>25</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -6232,22 +6232,22 @@
         <v>운전자B</v>
       </c>
       <c r="E41">
-        <v>685.5</v>
+        <v>676.5</v>
       </c>
       <c r="F41">
-        <v>693</v>
+        <v>684.5</v>
       </c>
       <c r="G41">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H41">
-        <v>21.1</v>
+        <v>28.2</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>IMG_20260824_3(예시).jpg</v>
       </c>
     </row>
     <row r="42">
@@ -6264,16 +6264,16 @@
         <v>운전자C</v>
       </c>
       <c r="E42">
-        <v>693</v>
+        <v>684.5</v>
       </c>
       <c r="F42">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="G42">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H42">
-        <v>19.2</v>
+        <v>20.8</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -6296,22 +6296,22 @@
         <v>운전자D</v>
       </c>
       <c r="E43">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="F43">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="G43">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H43">
-        <v>28.5</v>
+        <v>23.4</v>
       </c>
       <c r="I43" t="str">
-        <v>운전석 계기판 화면 깜빡임(예시)</v>
+        <v/>
       </c>
       <c r="J43" t="str">
-        <v>IMG_20260826_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -6328,16 +6328,16 @@
         <v>운전자A</v>
       </c>
       <c r="E44">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="F44">
-        <v>711.5</v>
+        <v>703.5</v>
       </c>
       <c r="G44">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H44">
-        <v>22.1</v>
+        <v>28.5</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -6360,22 +6360,22 @@
         <v>운전자B</v>
       </c>
       <c r="E45">
-        <v>711.5</v>
+        <v>703.5</v>
       </c>
       <c r="F45">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="G45">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H45">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="I45" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J45" t="str">
-        <v>IMG_20260828_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -6392,16 +6392,16 @@
         <v>운전자C</v>
       </c>
       <c r="E46">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="F46">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="G46">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H46">
-        <v>25</v>
+        <v>23.7</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -6424,22 +6424,22 @@
         <v>운전자D</v>
       </c>
       <c r="E47">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="F47">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="G47">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="H47">
-        <v>28.2</v>
+        <v>18.9</v>
       </c>
       <c r="I47" t="str">
-        <v>브레이크 페달 유격 커짐(예시)</v>
+        <v/>
       </c>
       <c r="J47" t="str">
-        <v>IMG_20260901_3(예시).jpg</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -6456,16 +6456,16 @@
         <v>운전자A</v>
       </c>
       <c r="E48">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="F48">
-        <v>738.5</v>
+        <v>730</v>
       </c>
       <c r="G48">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H48">
-        <v>20.8</v>
+        <v>28.2</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -6488,16 +6488,16 @@
         <v>운전자B</v>
       </c>
       <c r="E49">
-        <v>738.5</v>
+        <v>730</v>
       </c>
       <c r="F49">
-        <v>744.5</v>
+        <v>738</v>
       </c>
       <c r="G49">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H49">
-        <v>23.4</v>
+        <v>26.6</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -6520,16 +6520,16 @@
         <v>운전자C</v>
       </c>
       <c r="E50">
+        <v>738</v>
+      </c>
+      <c r="F50">
         <v>744.5</v>
       </c>
-      <c r="F50">
-        <v>752</v>
-      </c>
       <c r="G50">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="H50">
-        <v>28.5</v>
+        <v>19.5</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -6552,16 +6552,16 @@
         <v>운전자D</v>
       </c>
       <c r="E51">
-        <v>752</v>
+        <v>744.5</v>
       </c>
       <c r="F51">
-        <v>758.5</v>
+        <v>750</v>
       </c>
       <c r="G51">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H51">
-        <v>27.8</v>
+        <v>28.8</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -6584,16 +6584,16 @@
         <v>운전자A</v>
       </c>
       <c r="E52">
-        <v>758.5</v>
+        <v>750</v>
       </c>
       <c r="F52">
-        <v>764.5</v>
+        <v>756</v>
       </c>
       <c r="G52">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H52">
-        <v>23.7</v>
+        <v>20.5</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -6616,16 +6616,16 @@
         <v>운전자B</v>
       </c>
       <c r="E53">
-        <v>764.5</v>
+        <v>756</v>
       </c>
       <c r="F53">
-        <v>771.5</v>
+        <v>761.5</v>
       </c>
       <c r="G53">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H53">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -6648,10 +6648,10 @@
         <v>운전자C</v>
       </c>
       <c r="E54">
-        <v>771.5</v>
+        <v>761.5</v>
       </c>
       <c r="F54">
-        <v>778.5</v>
+        <v>768</v>
       </c>
       <c r="G54">
         <v>88</v>
@@ -6680,16 +6680,16 @@
         <v>운전자D</v>
       </c>
       <c r="E55">
-        <v>778.5</v>
+        <v>768</v>
       </c>
       <c r="F55">
-        <v>786.5</v>
+        <v>775.5</v>
       </c>
       <c r="G55">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H55">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -6712,16 +6712,16 @@
         <v>운전자A</v>
       </c>
       <c r="E56">
-        <v>786.5</v>
+        <v>775.5</v>
       </c>
       <c r="F56">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="G56">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H56">
-        <v>19.5</v>
+        <v>28.8</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -6744,16 +6744,16 @@
         <v>운전자B</v>
       </c>
       <c r="E57">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="F57">
-        <v>798.5</v>
+        <v>787</v>
       </c>
       <c r="G57">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="H57">
-        <v>28.8</v>
+        <v>18.6</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -6776,16 +6776,16 @@
         <v>운전자C</v>
       </c>
       <c r="E58">
-        <v>798.5</v>
+        <v>787</v>
       </c>
       <c r="F58">
-        <v>804.5</v>
+        <v>792.5</v>
       </c>
       <c r="G58">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H58">
-        <v>20.5</v>
+        <v>26.2</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -6808,16 +6808,16 @@
         <v>운전자D</v>
       </c>
       <c r="E59">
-        <v>804.5</v>
+        <v>792.5</v>
       </c>
       <c r="F59">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="G59">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="H59">
-        <v>19.2</v>
+        <v>28.5</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -6840,16 +6840,16 @@
         <v>운전자A</v>
       </c>
       <c r="E60">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="F60">
-        <v>816.5</v>
+        <v>805.5</v>
       </c>
       <c r="G60">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H60">
-        <v>28.2</v>
+        <v>25.9</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -6872,16 +6872,16 @@
         <v>운전자B</v>
       </c>
       <c r="E61">
-        <v>816.5</v>
+        <v>805.5</v>
       </c>
       <c r="F61">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="G61">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="H61">
-        <v>26.9</v>
+        <v>20.2</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -6904,16 +6904,16 @@
         <v>운전자C</v>
       </c>
       <c r="E62">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="F62">
-        <v>830.5</v>
+        <v>817</v>
       </c>
       <c r="G62">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="H62">
-        <v>28.8</v>
+        <v>20.2</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -6936,16 +6936,16 @@
         <v>운전자D</v>
       </c>
       <c r="E63">
-        <v>830.5</v>
+        <v>817</v>
       </c>
       <c r="F63">
-        <v>835.5</v>
+        <v>823.5</v>
       </c>
       <c r="G63">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="H63">
-        <v>18.6</v>
+        <v>27.8</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -6968,22 +6968,22 @@
         <v>운전자A</v>
       </c>
       <c r="E64">
-        <v>835.5</v>
+        <v>823.5</v>
       </c>
       <c r="F64">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="G64">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H64">
-        <v>26.2</v>
+        <v>28.5</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>브레이크 페달 유격 커짐(예시)</v>
       </c>
       <c r="J64" t="str">
-        <v/>
+        <v>IMG_20260924_3(예시).jpg</v>
       </c>
     </row>
     <row r="65">
@@ -7000,16 +7000,16 @@
         <v>운전자B</v>
       </c>
       <c r="E65">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="F65">
-        <v>847.5</v>
+        <v>835</v>
       </c>
       <c r="G65">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H65">
-        <v>28.5</v>
+        <v>20.8</v>
       </c>
       <c r="I65" t="str">
         <v/>
